--- a/codes/sankey diagram/sankey diagram table.xlsx
+++ b/codes/sankey diagram/sankey diagram table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ef8a85349dc97480/Articles/Review Article/4. ExplainableAI/codes/sankey diagram/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="78" documentId="11_B34909007FAD39B596D5B0631C74C5B797DBBA21" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7A548FF-A66D-4493-A938-F3B2C8665043}"/>
+  <xr:revisionPtr revIDLastSave="97" documentId="11_B34909007FAD39B596D5B0631C74C5B797DBBA21" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5ECFB12C-1DFF-408F-A147-C0A9805F169C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,8 +39,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3494" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3494" uniqueCount="309">
   <si>
     <t>selected article</t>
   </si>
@@ -964,6 +986,9 @@
   </si>
   <si>
     <t>XAI Methods Used_orginal</t>
+  </si>
+  <si>
+    <t>Citrus</t>
   </si>
 </sst>
 </file>
@@ -7832,7 +7857,7 @@
   <sheetPr>
     <tabColor theme="9"/>
   </sheetPr>
-  <dimension ref="A1:G334"/>
+  <dimension ref="A1:I334"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.140625" bestFit="1" customWidth="1"/>
@@ -7844,7 +7869,7 @@
     <col min="9" max="9" width="117.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -7867,21 +7892,21 @@
         <v>289</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>152</v>
       </c>
       <c r="B2" t="s">
-        <v>266</v>
+        <v>205</v>
       </c>
       <c r="C2" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="D2" t="s">
-        <v>267</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>267</v>
+        <v>14</v>
       </c>
       <c r="F2" t="s">
         <v>302</v>
@@ -7889,22 +7914,26 @@
       <c r="G2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I2" t="str" cm="1">
+        <f t="array" ref="I2:I36">_xlfn.UNIQUE(A2:A334)</f>
+        <v>Apple</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>152</v>
       </c>
       <c r="B3" t="s">
-        <v>271</v>
+        <v>203</v>
       </c>
       <c r="C3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D3" t="s">
-        <v>267</v>
+        <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>267</v>
+        <v>14</v>
       </c>
       <c r="F3" t="s">
         <v>302</v>
@@ -7912,22 +7941,25 @@
       <c r="G3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I3" t="str">
+        <v>Apricot</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>152</v>
       </c>
       <c r="B4" t="s">
-        <v>269</v>
+        <v>157</v>
       </c>
       <c r="C4" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>14</v>
       </c>
       <c r="E4" t="s">
-        <v>267</v>
+        <v>14</v>
       </c>
       <c r="F4" t="s">
         <v>302</v>
@@ -7935,22 +7967,25 @@
       <c r="G4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I4" t="str">
+        <v>Banana</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>152</v>
       </c>
       <c r="B5" t="s">
-        <v>270</v>
+        <v>204</v>
       </c>
       <c r="C5" t="s">
         <v>292</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>267</v>
+        <v>14</v>
       </c>
       <c r="F5" t="s">
         <v>302</v>
@@ -7958,22 +7993,25 @@
       <c r="G5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I5" t="str">
+        <v>Black Gram</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>152</v>
       </c>
       <c r="B6" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="C6" t="s">
         <v>292</v>
       </c>
       <c r="D6" t="s">
-        <v>267</v>
+        <v>14</v>
       </c>
       <c r="E6" t="s">
-        <v>267</v>
+        <v>14</v>
       </c>
       <c r="F6" t="s">
         <v>302</v>
@@ -7981,229 +8019,259 @@
       <c r="G6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I6" t="str">
+        <v>Bottle Gourd</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>152</v>
       </c>
       <c r="B7" t="s">
-        <v>273</v>
+        <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D7" t="s">
-        <v>274</v>
+        <v>14</v>
       </c>
       <c r="E7" t="s">
-        <v>274</v>
+        <v>14</v>
       </c>
       <c r="F7" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="G7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I7" t="str">
+        <v>Cassava</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>152</v>
       </c>
       <c r="B8" t="s">
-        <v>221</v>
+        <v>169</v>
       </c>
       <c r="C8" t="s">
         <v>292</v>
       </c>
       <c r="D8" t="s">
-        <v>274</v>
+        <v>14</v>
       </c>
       <c r="E8" t="s">
-        <v>274</v>
+        <v>14</v>
       </c>
       <c r="F8" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="G8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I8" t="str">
+        <v>Cherry</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>5</v>
+        <v>152</v>
       </c>
       <c r="B9" t="s">
-        <v>275</v>
+        <v>206</v>
       </c>
       <c r="C9" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="D9" t="s">
-        <v>274</v>
+        <v>14</v>
       </c>
       <c r="E9" t="s">
-        <v>274</v>
+        <v>14</v>
       </c>
       <c r="F9" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="G9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I9" t="str">
+        <v>Citrus</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>5</v>
+        <v>152</v>
       </c>
       <c r="B10" t="s">
-        <v>276</v>
+        <v>192</v>
       </c>
       <c r="C10" t="s">
         <v>292</v>
       </c>
       <c r="D10" t="s">
-        <v>274</v>
+        <v>134</v>
       </c>
       <c r="E10" t="s">
-        <v>274</v>
+        <v>134</v>
       </c>
       <c r="F10" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="I10" t="str">
+        <v>Coffee Cherry</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>5</v>
+        <v>152</v>
       </c>
       <c r="B11" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C11" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>134</v>
       </c>
       <c r="E11" t="s">
-        <v>274</v>
+        <v>134</v>
       </c>
       <c r="F11" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="G11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I11" t="str">
+        <v>Maize</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>5</v>
+        <v>152</v>
       </c>
       <c r="B12" t="s">
-        <v>9</v>
+        <v>189</v>
       </c>
       <c r="C12" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D12" t="s">
-        <v>10</v>
+        <v>134</v>
       </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>134</v>
       </c>
       <c r="F12" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G12">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I12" t="str">
+        <v>Cotton</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>80</v>
+        <v>152</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>191</v>
       </c>
       <c r="C13" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D13" t="s">
-        <v>215</v>
+        <v>134</v>
       </c>
       <c r="E13" t="s">
-        <v>215</v>
+        <v>134</v>
       </c>
       <c r="F13" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="I13" t="str">
+        <v>Cucumber</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>64</v>
+        <v>152</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>169</v>
       </c>
       <c r="C14" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D14" t="s">
-        <v>215</v>
+        <v>134</v>
       </c>
       <c r="E14" t="s">
-        <v>215</v>
+        <v>134</v>
       </c>
       <c r="F14" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G14">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I14" t="str">
+        <v>Eggplant (Insect Pests)</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>152</v>
       </c>
       <c r="B15" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="C15" t="s">
         <v>292</v>
       </c>
       <c r="D15" t="s">
-        <v>14</v>
+        <v>134</v>
       </c>
       <c r="E15" t="s">
-        <v>14</v>
+        <v>134</v>
       </c>
       <c r="F15" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G15">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I15" t="str">
+        <v>Faba bean</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>152</v>
       </c>
       <c r="B16" t="s">
-        <v>203</v>
+        <v>157</v>
       </c>
       <c r="C16" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D16" t="s">
-        <v>14</v>
+        <v>209</v>
       </c>
       <c r="E16" t="s">
-        <v>14</v>
+        <v>209</v>
       </c>
       <c r="F16" t="s">
         <v>302</v>
@@ -8211,22 +8279,25 @@
       <c r="G16">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I16" t="str">
+        <v>Fabric</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>152</v>
       </c>
       <c r="B17" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C17" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D17" t="s">
-        <v>14</v>
+        <v>194</v>
       </c>
       <c r="E17" t="s">
-        <v>14</v>
+        <v>194</v>
       </c>
       <c r="F17" t="s">
         <v>302</v>
@@ -8234,123 +8305,141 @@
       <c r="G17">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I17" t="str">
+        <v>Grapevine</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>152</v>
       </c>
       <c r="B18" t="s">
-        <v>204</v>
+        <v>169</v>
       </c>
       <c r="C18" t="s">
         <v>292</v>
       </c>
       <c r="D18" t="s">
-        <v>14</v>
+        <v>162</v>
       </c>
       <c r="E18" t="s">
-        <v>14</v>
+        <v>162</v>
       </c>
       <c r="F18" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G18">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I18" t="str">
+        <v>Guava</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>152</v>
       </c>
       <c r="B19" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="C19" t="s">
         <v>292</v>
       </c>
       <c r="D19" t="s">
-        <v>14</v>
+        <v>190</v>
       </c>
       <c r="E19" t="s">
-        <v>14</v>
+        <v>190</v>
       </c>
       <c r="F19" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="G19">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I19" t="str">
+        <v>Insect Pests</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>152</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>189</v>
       </c>
       <c r="C20" t="s">
         <v>292</v>
       </c>
       <c r="D20" t="s">
-        <v>14</v>
+        <v>190</v>
       </c>
       <c r="E20" t="s">
-        <v>14</v>
+        <v>190</v>
       </c>
       <c r="F20" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="G20">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I20" t="str">
+        <v>Jute</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>152</v>
       </c>
       <c r="B21" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="C21" t="s">
         <v>292</v>
       </c>
       <c r="D21" t="s">
-        <v>14</v>
+        <v>190</v>
       </c>
       <c r="E21" t="s">
-        <v>14</v>
+        <v>190</v>
       </c>
       <c r="F21" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="G21">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I21" t="str">
+        <v>Mango</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>152</v>
       </c>
       <c r="B22" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="C22" t="s">
         <v>292</v>
       </c>
       <c r="D22" t="s">
-        <v>14</v>
+        <v>190</v>
       </c>
       <c r="E22" t="s">
-        <v>14</v>
+        <v>190</v>
       </c>
       <c r="F22" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="G22">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I22" t="str">
+        <v>Mulberry</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>195</v>
       </c>
@@ -8372,45 +8461,51 @@
       <c r="G23">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I23" t="str">
+        <v>Oat</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>48</v>
+        <v>195</v>
       </c>
       <c r="B24" t="s">
-        <v>211</v>
+        <v>169</v>
       </c>
       <c r="C24" t="s">
         <v>292</v>
       </c>
       <c r="D24" t="s">
-        <v>14</v>
+        <v>134</v>
       </c>
       <c r="E24" t="s">
-        <v>14</v>
+        <v>134</v>
       </c>
       <c r="F24" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G24">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I24" t="str">
+        <v>Others</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>48</v>
+        <v>195</v>
       </c>
       <c r="B25" t="s">
-        <v>206</v>
+        <v>169</v>
       </c>
       <c r="C25" t="s">
         <v>292</v>
       </c>
       <c r="D25" t="s">
-        <v>14</v>
+        <v>194</v>
       </c>
       <c r="E25" t="s">
-        <v>14</v>
+        <v>194</v>
       </c>
       <c r="F25" t="s">
         <v>302</v>
@@ -8418,128 +8513,146 @@
       <c r="G25">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I25" t="str">
+        <v>Papaya</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>48</v>
+        <v>195</v>
       </c>
       <c r="B26" t="s">
-        <v>210</v>
+        <v>169</v>
       </c>
       <c r="C26" t="s">
         <v>292</v>
       </c>
       <c r="D26" t="s">
-        <v>14</v>
+        <v>162</v>
       </c>
       <c r="E26" t="s">
-        <v>14</v>
+        <v>162</v>
       </c>
       <c r="F26" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G26">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I26" t="str">
+        <v>Peach</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>48</v>
       </c>
       <c r="B27" t="s">
+        <v>211</v>
+      </c>
+      <c r="C27" t="s">
+        <v>292</v>
+      </c>
+      <c r="D27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" t="s">
+        <v>14</v>
+      </c>
+      <c r="F27" t="s">
+        <v>302</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="I27" t="str">
+        <v>Pear</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>48</v>
+      </c>
+      <c r="B28" t="s">
+        <v>206</v>
+      </c>
+      <c r="C28" t="s">
+        <v>292</v>
+      </c>
+      <c r="D28" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" t="s">
+        <v>14</v>
+      </c>
+      <c r="F28" t="s">
+        <v>302</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+      <c r="I28" t="str">
+        <v>Pomegranate</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>48</v>
+      </c>
+      <c r="B29" t="s">
+        <v>210</v>
+      </c>
+      <c r="C29" t="s">
+        <v>292</v>
+      </c>
+      <c r="D29" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" t="s">
+        <v>14</v>
+      </c>
+      <c r="F29" t="s">
+        <v>302</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+      <c r="I29" t="str">
+        <v>Potato</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>48</v>
+      </c>
+      <c r="B30" t="s">
         <v>212</v>
       </c>
-      <c r="C27" t="s">
-        <v>292</v>
-      </c>
-      <c r="D27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E27" t="s">
-        <v>14</v>
-      </c>
-      <c r="F27" t="s">
-        <v>302</v>
-      </c>
-      <c r="G27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="C30" t="s">
+        <v>292</v>
+      </c>
+      <c r="D30" t="s">
+        <v>14</v>
+      </c>
+      <c r="E30" t="s">
+        <v>14</v>
+      </c>
+      <c r="F30" t="s">
+        <v>302</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+      <c r="I30" t="str">
+        <v>Rice</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>213</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B31" t="s">
         <v>69</v>
-      </c>
-      <c r="C28" t="s">
-        <v>293</v>
-      </c>
-      <c r="D28" t="s">
-        <v>14</v>
-      </c>
-      <c r="E28" t="s">
-        <v>14</v>
-      </c>
-      <c r="F28" t="s">
-        <v>302</v>
-      </c>
-      <c r="G28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>80</v>
-      </c>
-      <c r="B29" t="s">
-        <v>81</v>
-      </c>
-      <c r="C29" t="s">
-        <v>294</v>
-      </c>
-      <c r="D29" t="s">
-        <v>14</v>
-      </c>
-      <c r="E29" t="s">
-        <v>14</v>
-      </c>
-      <c r="F29" t="s">
-        <v>302</v>
-      </c>
-      <c r="G29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>12</v>
-      </c>
-      <c r="B30" t="s">
-        <v>13</v>
-      </c>
-      <c r="C30" t="s">
-        <v>292</v>
-      </c>
-      <c r="D30" t="s">
-        <v>14</v>
-      </c>
-      <c r="E30" t="s">
-        <v>14</v>
-      </c>
-      <c r="F30" t="s">
-        <v>302</v>
-      </c>
-      <c r="G30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>251</v>
-      </c>
-      <c r="B31" t="s">
-        <v>17</v>
       </c>
       <c r="C31" t="s">
         <v>293</v>
@@ -8556,22 +8669,25 @@
       <c r="G31">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I31" t="str">
+        <v>Soursop</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>132</v>
+        <v>213</v>
       </c>
       <c r="B32" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C32" t="s">
         <v>293</v>
       </c>
       <c r="D32" t="s">
-        <v>14</v>
+        <v>124</v>
       </c>
       <c r="E32" t="s">
-        <v>14</v>
+        <v>124</v>
       </c>
       <c r="F32" t="s">
         <v>302</v>
@@ -8579,370 +8695,385 @@
       <c r="G32">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I32" t="str">
+        <v>Soybean</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="B33" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C33" t="s">
         <v>293</v>
       </c>
       <c r="D33" t="s">
-        <v>14</v>
+        <v>134</v>
       </c>
       <c r="E33" t="s">
-        <v>14</v>
+        <v>134</v>
       </c>
       <c r="F33" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G33">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I33" t="str">
+        <v>Strawberry</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>144</v>
+        <v>80</v>
       </c>
       <c r="B34" t="s">
+        <v>81</v>
+      </c>
+      <c r="C34" t="s">
+        <v>294</v>
+      </c>
+      <c r="D34" t="s">
+        <v>215</v>
+      </c>
+      <c r="E34" t="s">
+        <v>215</v>
+      </c>
+      <c r="F34" t="s">
+        <v>302</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+      <c r="I34" t="str">
+        <v>Tomato</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>80</v>
+      </c>
+      <c r="B35" t="s">
+        <v>81</v>
+      </c>
+      <c r="C35" t="s">
+        <v>294</v>
+      </c>
+      <c r="D35" t="s">
+        <v>14</v>
+      </c>
+      <c r="E35" t="s">
+        <v>14</v>
+      </c>
+      <c r="F35" t="s">
+        <v>302</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+      <c r="I35" t="str">
+        <v>Walnut</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>80</v>
+      </c>
+      <c r="B36" t="s">
+        <v>81</v>
+      </c>
+      <c r="C36" t="s">
+        <v>294</v>
+      </c>
+      <c r="D36" t="s">
+        <v>124</v>
+      </c>
+      <c r="E36" t="s">
+        <v>124</v>
+      </c>
+      <c r="F36" t="s">
+        <v>302</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+      <c r="I36" t="str">
+        <v>Wheat</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>80</v>
+      </c>
+      <c r="B37" t="s">
+        <v>81</v>
+      </c>
+      <c r="C37" t="s">
+        <v>294</v>
+      </c>
+      <c r="D37" t="s">
+        <v>214</v>
+      </c>
+      <c r="E37" t="s">
+        <v>214</v>
+      </c>
+      <c r="F37" t="s">
+        <v>302</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>12</v>
+      </c>
+      <c r="B38" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" t="s">
+        <v>292</v>
+      </c>
+      <c r="D38" t="s">
+        <v>14</v>
+      </c>
+      <c r="E38" t="s">
+        <v>14</v>
+      </c>
+      <c r="F38" t="s">
+        <v>302</v>
+      </c>
+      <c r="G38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>251</v>
+      </c>
+      <c r="B39" t="s">
+        <v>17</v>
+      </c>
+      <c r="C39" t="s">
+        <v>293</v>
+      </c>
+      <c r="D39" t="s">
+        <v>14</v>
+      </c>
+      <c r="E39" t="s">
+        <v>14</v>
+      </c>
+      <c r="F39" t="s">
+        <v>302</v>
+      </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>308</v>
+      </c>
+      <c r="B40" t="s">
+        <v>73</v>
+      </c>
+      <c r="C40" t="s">
+        <v>293</v>
+      </c>
+      <c r="D40" t="s">
+        <v>14</v>
+      </c>
+      <c r="E40" t="s">
+        <v>14</v>
+      </c>
+      <c r="F40" t="s">
+        <v>302</v>
+      </c>
+      <c r="G40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>308</v>
+      </c>
+      <c r="B41" t="s">
+        <v>73</v>
+      </c>
+      <c r="C41" t="s">
+        <v>293</v>
+      </c>
+      <c r="D41" t="s">
+        <v>124</v>
+      </c>
+      <c r="E41" t="s">
+        <v>124</v>
+      </c>
+      <c r="F41" t="s">
+        <v>302</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>308</v>
+      </c>
+      <c r="B42" t="s">
+        <v>133</v>
+      </c>
+      <c r="C42" t="s">
+        <v>293</v>
+      </c>
+      <c r="D42" t="s">
+        <v>134</v>
+      </c>
+      <c r="E42" t="s">
+        <v>134</v>
+      </c>
+      <c r="F42" t="s">
+        <v>303</v>
+      </c>
+      <c r="G42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>308</v>
+      </c>
+      <c r="B43" t="s">
+        <v>73</v>
+      </c>
+      <c r="C43" t="s">
+        <v>293</v>
+      </c>
+      <c r="D43" t="s">
+        <v>134</v>
+      </c>
+      <c r="E43" t="s">
+        <v>134</v>
+      </c>
+      <c r="F43" t="s">
+        <v>303</v>
+      </c>
+      <c r="G43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>308</v>
+      </c>
+      <c r="B44" t="s">
+        <v>73</v>
+      </c>
+      <c r="C44" t="s">
+        <v>293</v>
+      </c>
+      <c r="D44" t="s">
+        <v>14</v>
+      </c>
+      <c r="E44" t="s">
+        <v>14</v>
+      </c>
+      <c r="F44" t="s">
+        <v>302</v>
+      </c>
+      <c r="G44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>308</v>
+      </c>
+      <c r="B45" t="s">
         <v>145</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C45" t="s">
         <v>293</v>
       </c>
-      <c r="D34" t="s">
-        <v>14</v>
-      </c>
-      <c r="E34" t="s">
-        <v>14</v>
-      </c>
-      <c r="F34" t="s">
-        <v>302</v>
-      </c>
-      <c r="G34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>199</v>
-      </c>
-      <c r="B35" t="s">
-        <v>69</v>
-      </c>
-      <c r="C35" t="s">
+      <c r="D45" t="s">
+        <v>14</v>
+      </c>
+      <c r="E45" t="s">
+        <v>14</v>
+      </c>
+      <c r="F45" t="s">
+        <v>302</v>
+      </c>
+      <c r="G45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>308</v>
+      </c>
+      <c r="B46" t="s">
+        <v>73</v>
+      </c>
+      <c r="C46" t="s">
         <v>293</v>
       </c>
-      <c r="D35" t="s">
-        <v>14</v>
-      </c>
-      <c r="E35" t="s">
-        <v>14</v>
-      </c>
-      <c r="F35" t="s">
-        <v>302</v>
-      </c>
-      <c r="G35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>199</v>
-      </c>
-      <c r="B36" t="s">
-        <v>40</v>
-      </c>
-      <c r="C36" t="s">
-        <v>292</v>
-      </c>
-      <c r="D36" t="s">
-        <v>14</v>
-      </c>
-      <c r="E36" t="s">
-        <v>14</v>
-      </c>
-      <c r="F36" t="s">
-        <v>302</v>
-      </c>
-      <c r="G36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>60</v>
-      </c>
-      <c r="B37" t="s">
-        <v>88</v>
-      </c>
-      <c r="C37" t="s">
+      <c r="D46" t="s">
+        <v>124</v>
+      </c>
+      <c r="E46" t="s">
+        <v>124</v>
+      </c>
+      <c r="F46" t="s">
+        <v>302</v>
+      </c>
+      <c r="G46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>308</v>
+      </c>
+      <c r="B47" t="s">
+        <v>73</v>
+      </c>
+      <c r="C47" t="s">
         <v>293</v>
       </c>
-      <c r="D37" t="s">
-        <v>14</v>
-      </c>
-      <c r="E37" t="s">
-        <v>14</v>
-      </c>
-      <c r="F37" t="s">
-        <v>302</v>
-      </c>
-      <c r="G37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>60</v>
-      </c>
-      <c r="B38" t="s">
-        <v>84</v>
-      </c>
-      <c r="C38" t="s">
+      <c r="D47" t="s">
+        <v>134</v>
+      </c>
+      <c r="E47" t="s">
+        <v>134</v>
+      </c>
+      <c r="F47" t="s">
+        <v>303</v>
+      </c>
+      <c r="G47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>308</v>
+      </c>
+      <c r="B48" t="s">
+        <v>145</v>
+      </c>
+      <c r="C48" t="s">
         <v>293</v>
       </c>
-      <c r="D38" t="s">
-        <v>14</v>
-      </c>
-      <c r="E38" t="s">
-        <v>14</v>
-      </c>
-      <c r="F38" t="s">
-        <v>302</v>
-      </c>
-      <c r="G38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>60</v>
-      </c>
-      <c r="B39" t="s">
-        <v>218</v>
-      </c>
-      <c r="C39" t="s">
-        <v>294</v>
-      </c>
-      <c r="D39" t="s">
-        <v>14</v>
-      </c>
-      <c r="E39" t="s">
-        <v>14</v>
-      </c>
-      <c r="F39" t="s">
-        <v>302</v>
-      </c>
-      <c r="G39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>60</v>
-      </c>
-      <c r="B40" t="s">
-        <v>221</v>
-      </c>
-      <c r="C40" t="s">
-        <v>292</v>
-      </c>
-      <c r="D40" t="s">
-        <v>14</v>
-      </c>
-      <c r="E40" t="s">
-        <v>14</v>
-      </c>
-      <c r="F40" t="s">
-        <v>302</v>
-      </c>
-      <c r="G40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>60</v>
-      </c>
-      <c r="B41" t="s">
-        <v>28</v>
-      </c>
-      <c r="C41" t="s">
-        <v>296</v>
-      </c>
-      <c r="D41" t="s">
-        <v>14</v>
-      </c>
-      <c r="E41" t="s">
-        <v>14</v>
-      </c>
-      <c r="F41" t="s">
-        <v>302</v>
-      </c>
-      <c r="G41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>60</v>
-      </c>
-      <c r="B42" t="s">
-        <v>220</v>
-      </c>
-      <c r="C42" t="s">
-        <v>292</v>
-      </c>
-      <c r="D42" t="s">
-        <v>14</v>
-      </c>
-      <c r="E42" t="s">
-        <v>14</v>
-      </c>
-      <c r="F42" t="s">
-        <v>302</v>
-      </c>
-      <c r="G42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>60</v>
-      </c>
-      <c r="B43" t="s">
-        <v>219</v>
-      </c>
-      <c r="C43" t="s">
-        <v>292</v>
-      </c>
-      <c r="D43" t="s">
-        <v>14</v>
-      </c>
-      <c r="E43" t="s">
-        <v>14</v>
-      </c>
-      <c r="F43" t="s">
-        <v>302</v>
-      </c>
-      <c r="G43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>64</v>
-      </c>
-      <c r="B44" t="s">
-        <v>65</v>
-      </c>
-      <c r="C44" t="s">
-        <v>294</v>
-      </c>
-      <c r="D44" t="s">
-        <v>14</v>
-      </c>
-      <c r="E44" t="s">
-        <v>14</v>
-      </c>
-      <c r="F44" t="s">
-        <v>302</v>
-      </c>
-      <c r="G44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>223</v>
-      </c>
-      <c r="B45" t="s">
-        <v>28</v>
-      </c>
-      <c r="C45" t="s">
-        <v>296</v>
-      </c>
-      <c r="D45" t="s">
-        <v>14</v>
-      </c>
-      <c r="E45" t="s">
-        <v>14</v>
-      </c>
-      <c r="F45" t="s">
-        <v>302</v>
-      </c>
-      <c r="G45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>200</v>
-      </c>
-      <c r="B46" t="s">
-        <v>40</v>
-      </c>
-      <c r="C46" t="s">
-        <v>292</v>
-      </c>
-      <c r="D46" t="s">
-        <v>14</v>
-      </c>
-      <c r="E46" t="s">
-        <v>14</v>
-      </c>
-      <c r="F46" t="s">
-        <v>302</v>
-      </c>
-      <c r="G46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>118</v>
-      </c>
-      <c r="B47" t="s">
-        <v>224</v>
-      </c>
-      <c r="C47" t="s">
-        <v>292</v>
-      </c>
-      <c r="D47" t="s">
-        <v>14</v>
-      </c>
-      <c r="E47" t="s">
-        <v>14</v>
-      </c>
-      <c r="F47" t="s">
-        <v>302</v>
-      </c>
-      <c r="G47">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>118</v>
-      </c>
-      <c r="B48" t="s">
-        <v>226</v>
-      </c>
-      <c r="C48" t="s">
-        <v>292</v>
-      </c>
       <c r="D48" t="s">
-        <v>14</v>
+        <v>134</v>
       </c>
       <c r="E48" t="s">
-        <v>14</v>
+        <v>134</v>
       </c>
       <c r="F48" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G48">
         <v>1</v>
@@ -8950,19 +9081,19 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>118</v>
+        <v>308</v>
       </c>
       <c r="B49" t="s">
-        <v>227</v>
+        <v>145</v>
       </c>
       <c r="C49" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D49" t="s">
-        <v>14</v>
+        <v>214</v>
       </c>
       <c r="E49" t="s">
-        <v>14</v>
+        <v>214</v>
       </c>
       <c r="F49" t="s">
         <v>302</v>
@@ -8973,22 +9104,22 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>118</v>
+        <v>160</v>
       </c>
       <c r="B50" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="C50" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="D50" t="s">
-        <v>14</v>
+        <v>162</v>
       </c>
       <c r="E50" t="s">
-        <v>14</v>
+        <v>162</v>
       </c>
       <c r="F50" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G50">
         <v>1</v>
@@ -8996,22 +9127,22 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>118</v>
+        <v>160</v>
       </c>
       <c r="B51" t="s">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="C51" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="D51" t="s">
-        <v>14</v>
+        <v>162</v>
       </c>
       <c r="E51" t="s">
-        <v>14</v>
+        <v>162</v>
       </c>
       <c r="F51" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G51">
         <v>1</v>
@@ -9019,13 +9150,13 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>36</v>
+        <v>288</v>
       </c>
       <c r="B52" t="s">
-        <v>205</v>
+        <v>69</v>
       </c>
       <c r="C52" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D52" t="s">
         <v>14</v>
@@ -9042,13 +9173,13 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>36</v>
+        <v>288</v>
       </c>
       <c r="B53" t="s">
-        <v>203</v>
+        <v>40</v>
       </c>
       <c r="C53" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D53" t="s">
         <v>14</v>
@@ -9065,19 +9196,19 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>36</v>
+        <v>288</v>
       </c>
       <c r="B54" t="s">
-        <v>192</v>
+        <v>69</v>
       </c>
       <c r="C54" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D54" t="s">
-        <v>14</v>
+        <v>124</v>
       </c>
       <c r="E54" t="s">
-        <v>14</v>
+        <v>124</v>
       </c>
       <c r="F54" t="s">
         <v>302</v>
@@ -9088,22 +9219,22 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>36</v>
+        <v>288</v>
       </c>
       <c r="B55" t="s">
-        <v>204</v>
+        <v>69</v>
       </c>
       <c r="C55" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D55" t="s">
-        <v>14</v>
+        <v>134</v>
       </c>
       <c r="E55" t="s">
-        <v>14</v>
+        <v>134</v>
       </c>
       <c r="F55" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G55">
         <v>1</v>
@@ -9111,22 +9242,22 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>36</v>
+        <v>288</v>
       </c>
       <c r="B56" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="C56" t="s">
         <v>292</v>
       </c>
       <c r="D56" t="s">
-        <v>14</v>
+        <v>134</v>
       </c>
       <c r="E56" t="s">
-        <v>14</v>
+        <v>134</v>
       </c>
       <c r="F56" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G56">
         <v>1</v>
@@ -9134,22 +9265,22 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>36</v>
+        <v>288</v>
       </c>
       <c r="B57" t="s">
-        <v>229</v>
+        <v>202</v>
       </c>
       <c r="C57" t="s">
         <v>294</v>
       </c>
       <c r="D57" t="s">
-        <v>14</v>
+        <v>134</v>
       </c>
       <c r="E57" t="s">
-        <v>14</v>
+        <v>134</v>
       </c>
       <c r="F57" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G57">
         <v>1</v>
@@ -9157,22 +9288,22 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>36</v>
+        <v>288</v>
       </c>
       <c r="B58" t="s">
-        <v>230</v>
+        <v>191</v>
       </c>
       <c r="C58" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="D58" t="s">
-        <v>14</v>
+        <v>134</v>
       </c>
       <c r="E58" t="s">
-        <v>14</v>
+        <v>134</v>
       </c>
       <c r="F58" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G58">
         <v>1</v>
@@ -9180,13 +9311,13 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>206</v>
+        <v>88</v>
       </c>
       <c r="C59" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D59" t="s">
         <v>14</v>
@@ -9203,13 +9334,13 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="B60" t="s">
-        <v>233</v>
+        <v>84</v>
       </c>
       <c r="C60" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D60" t="s">
         <v>14</v>
@@ -9226,13 +9357,13 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="C61" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D61" t="s">
         <v>14</v>
@@ -9249,10 +9380,10 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="C62" t="s">
         <v>292</v>
@@ -9272,13 +9403,13 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="B63" t="s">
-        <v>193</v>
+        <v>28</v>
       </c>
       <c r="C63" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D63" t="s">
         <v>14</v>
@@ -9295,13 +9426,13 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>234</v>
+        <v>60</v>
       </c>
       <c r="B64" t="s">
-        <v>25</v>
+        <v>220</v>
       </c>
       <c r="C64" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D64" t="s">
         <v>14</v>
@@ -9318,13 +9449,13 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>288</v>
+        <v>60</v>
       </c>
       <c r="B65" t="s">
-        <v>88</v>
+        <v>219</v>
       </c>
       <c r="C65" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D65" t="s">
         <v>14</v>
@@ -9341,19 +9472,19 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="B66" t="s">
-        <v>236</v>
+        <v>84</v>
       </c>
       <c r="C66" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D66" t="s">
-        <v>14</v>
+        <v>124</v>
       </c>
       <c r="E66" t="s">
-        <v>14</v>
+        <v>124</v>
       </c>
       <c r="F66" t="s">
         <v>302</v>
@@ -9364,19 +9495,19 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="B67" t="s">
-        <v>113</v>
+        <v>218</v>
       </c>
       <c r="C67" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D67" t="s">
-        <v>14</v>
+        <v>124</v>
       </c>
       <c r="E67" t="s">
-        <v>14</v>
+        <v>124</v>
       </c>
       <c r="F67" t="s">
         <v>302</v>
@@ -9387,19 +9518,19 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="B68" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="C68" t="s">
         <v>292</v>
       </c>
       <c r="D68" t="s">
-        <v>14</v>
+        <v>124</v>
       </c>
       <c r="E68" t="s">
-        <v>14</v>
+        <v>124</v>
       </c>
       <c r="F68" t="s">
         <v>302</v>
@@ -9410,7 +9541,7 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="B69" t="s">
         <v>220</v>
@@ -9419,10 +9550,10 @@
         <v>292</v>
       </c>
       <c r="D69" t="s">
-        <v>14</v>
+        <v>124</v>
       </c>
       <c r="E69" t="s">
-        <v>14</v>
+        <v>124</v>
       </c>
       <c r="F69" t="s">
         <v>302</v>
@@ -9433,19 +9564,19 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="B70" t="s">
-        <v>43</v>
+        <v>219</v>
       </c>
       <c r="C70" t="s">
         <v>292</v>
       </c>
       <c r="D70" t="s">
-        <v>14</v>
+        <v>124</v>
       </c>
       <c r="E70" t="s">
-        <v>14</v>
+        <v>124</v>
       </c>
       <c r="F70" t="s">
         <v>302</v>
@@ -9456,19 +9587,19 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="B71" t="s">
-        <v>230</v>
+        <v>88</v>
       </c>
       <c r="C71" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D71" t="s">
-        <v>14</v>
+        <v>278</v>
       </c>
       <c r="E71" t="s">
-        <v>14</v>
+        <v>278</v>
       </c>
       <c r="F71" t="s">
         <v>302</v>
@@ -9479,19 +9610,19 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="B72" t="s">
-        <v>193</v>
+        <v>88</v>
       </c>
       <c r="C72" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D72" t="s">
-        <v>14</v>
+        <v>287</v>
       </c>
       <c r="E72" t="s">
-        <v>14</v>
+        <v>287</v>
       </c>
       <c r="F72" t="s">
         <v>302</v>
@@ -9502,19 +9633,19 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="B73" t="s">
-        <v>205</v>
+        <v>84</v>
       </c>
       <c r="C73" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D73" t="s">
-        <v>14</v>
+        <v>214</v>
       </c>
       <c r="E73" t="s">
-        <v>14</v>
+        <v>214</v>
       </c>
       <c r="F73" t="s">
         <v>302</v>
@@ -9525,19 +9656,19 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="B74" t="s">
-        <v>203</v>
+        <v>84</v>
       </c>
       <c r="C74" t="s">
         <v>293</v>
       </c>
       <c r="D74" t="s">
-        <v>14</v>
+        <v>222</v>
       </c>
       <c r="E74" t="s">
-        <v>14</v>
+        <v>222</v>
       </c>
       <c r="F74" t="s">
         <v>302</v>
@@ -9548,19 +9679,19 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="B75" t="s">
-        <v>91</v>
+        <v>65</v>
       </c>
       <c r="C75" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D75" t="s">
-        <v>14</v>
+        <v>215</v>
       </c>
       <c r="E75" t="s">
-        <v>14</v>
+        <v>215</v>
       </c>
       <c r="F75" t="s">
         <v>302</v>
@@ -9571,13 +9702,13 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="B76" t="s">
-        <v>204</v>
+        <v>65</v>
       </c>
       <c r="C76" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D76" t="s">
         <v>14</v>
@@ -9594,19 +9725,19 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="B77" t="s">
-        <v>207</v>
+        <v>65</v>
       </c>
       <c r="C77" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D77" t="s">
-        <v>14</v>
+        <v>124</v>
       </c>
       <c r="E77" t="s">
-        <v>14</v>
+        <v>124</v>
       </c>
       <c r="F77" t="s">
         <v>302</v>
@@ -9617,22 +9748,22 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>33</v>
+        <v>264</v>
       </c>
       <c r="B78" t="s">
-        <v>34</v>
+        <v>262</v>
       </c>
       <c r="C78" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="D78" t="s">
-        <v>14</v>
+        <v>261</v>
       </c>
       <c r="E78" t="s">
-        <v>14</v>
+        <v>261</v>
       </c>
       <c r="F78" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G78">
         <v>1</v>
@@ -9640,22 +9771,22 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>33</v>
+        <v>264</v>
       </c>
       <c r="B79" t="s">
-        <v>206</v>
+        <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D79" t="s">
-        <v>14</v>
+        <v>261</v>
       </c>
       <c r="E79" t="s">
-        <v>14</v>
+        <v>261</v>
       </c>
       <c r="F79" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G79">
         <v>1</v>
@@ -9663,22 +9794,22 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>164</v>
+        <v>264</v>
       </c>
       <c r="B80" t="s">
-        <v>242</v>
+        <v>263</v>
       </c>
       <c r="C80" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="D80" t="s">
-        <v>14</v>
+        <v>261</v>
       </c>
       <c r="E80" t="s">
-        <v>14</v>
+        <v>261</v>
       </c>
       <c r="F80" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G80">
         <v>1</v>
@@ -9686,22 +9817,22 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>164</v>
+        <v>264</v>
       </c>
       <c r="B81" t="s">
-        <v>25</v>
+        <v>258</v>
       </c>
       <c r="C81" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D81" t="s">
-        <v>14</v>
+        <v>261</v>
       </c>
       <c r="E81" t="s">
-        <v>14</v>
+        <v>261</v>
       </c>
       <c r="F81" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G81">
         <v>1</v>
@@ -9709,22 +9840,22 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>164</v>
+        <v>264</v>
       </c>
       <c r="B82" t="s">
-        <v>243</v>
+        <v>262</v>
       </c>
       <c r="C82" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="D82" t="s">
-        <v>14</v>
+        <v>162</v>
       </c>
       <c r="E82" t="s">
-        <v>14</v>
+        <v>162</v>
       </c>
       <c r="F82" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G82">
         <v>1</v>
@@ -9732,22 +9863,22 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>208</v>
+        <v>264</v>
       </c>
       <c r="B83" t="s">
-        <v>205</v>
+        <v>260</v>
       </c>
       <c r="C83" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D83" t="s">
-        <v>14</v>
+        <v>162</v>
       </c>
       <c r="E83" t="s">
-        <v>14</v>
+        <v>162</v>
       </c>
       <c r="F83" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G83">
         <v>1</v>
@@ -9755,22 +9886,22 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>208</v>
+        <v>264</v>
       </c>
       <c r="B84" t="s">
-        <v>203</v>
+        <v>263</v>
       </c>
       <c r="C84" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D84" t="s">
-        <v>14</v>
+        <v>162</v>
       </c>
       <c r="E84" t="s">
-        <v>14</v>
+        <v>162</v>
       </c>
       <c r="F84" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G84">
         <v>1</v>
@@ -9778,22 +9909,22 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>208</v>
+        <v>264</v>
       </c>
       <c r="B85" t="s">
-        <v>204</v>
+        <v>258</v>
       </c>
       <c r="C85" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="D85" t="s">
-        <v>14</v>
+        <v>162</v>
       </c>
       <c r="E85" t="s">
-        <v>14</v>
+        <v>162</v>
       </c>
       <c r="F85" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G85">
         <v>1</v>
@@ -9801,22 +9932,22 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>208</v>
+        <v>265</v>
       </c>
       <c r="B86" t="s">
-        <v>207</v>
+        <v>179</v>
       </c>
       <c r="C86" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="D86" t="s">
-        <v>14</v>
+        <v>256</v>
       </c>
       <c r="E86" t="s">
-        <v>14</v>
+        <v>261</v>
       </c>
       <c r="F86" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G86">
         <v>1</v>
@@ -9824,22 +9955,22 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>208</v>
+        <v>265</v>
       </c>
       <c r="B87" t="s">
-        <v>206</v>
+        <v>179</v>
       </c>
       <c r="C87" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="D87" t="s">
-        <v>14</v>
+        <v>162</v>
       </c>
       <c r="E87" t="s">
-        <v>14</v>
+        <v>162</v>
       </c>
       <c r="F87" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G87">
         <v>1</v>
@@ -9847,13 +9978,13 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>105</v>
+        <v>223</v>
       </c>
       <c r="B88" t="s">
-        <v>106</v>
+        <v>28</v>
       </c>
       <c r="C88" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D88" t="s">
         <v>14</v>
@@ -9870,13 +10001,13 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="B89" t="s">
-        <v>116</v>
+        <v>40</v>
       </c>
       <c r="C89" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D89" t="s">
         <v>14</v>
@@ -9893,22 +10024,22 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="B90" t="s">
-        <v>95</v>
+        <v>192</v>
       </c>
       <c r="C90" t="s">
         <v>292</v>
       </c>
       <c r="D90" t="s">
-        <v>14</v>
+        <v>134</v>
       </c>
       <c r="E90" t="s">
-        <v>14</v>
+        <v>134</v>
       </c>
       <c r="F90" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G90">
         <v>1</v>
@@ -9916,22 +10047,22 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>196</v>
+        <v>118</v>
       </c>
       <c r="B91" t="s">
-        <v>17</v>
+        <v>202</v>
       </c>
       <c r="C91" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D91" t="s">
-        <v>14</v>
+        <v>134</v>
       </c>
       <c r="E91" t="s">
-        <v>14</v>
+        <v>134</v>
       </c>
       <c r="F91" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G91">
         <v>1</v>
@@ -9939,22 +10070,22 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>196</v>
+        <v>118</v>
       </c>
       <c r="B92" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="C92" t="s">
         <v>292</v>
       </c>
       <c r="D92" t="s">
-        <v>14</v>
+        <v>134</v>
       </c>
       <c r="E92" t="s">
-        <v>14</v>
+        <v>134</v>
       </c>
       <c r="F92" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G92">
         <v>1</v>
@@ -9962,10 +10093,10 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>197</v>
+        <v>118</v>
       </c>
       <c r="B93" t="s">
-        <v>169</v>
+        <v>224</v>
       </c>
       <c r="C93" t="s">
         <v>292</v>
@@ -9985,13 +10116,13 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>77</v>
+        <v>118</v>
       </c>
       <c r="B94" t="s">
-        <v>78</v>
+        <v>226</v>
       </c>
       <c r="C94" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D94" t="s">
         <v>14</v>
@@ -10008,10 +10139,10 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B95" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="C95" t="s">
         <v>292</v>
@@ -10031,13 +10162,13 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B96" t="s">
-        <v>203</v>
+        <v>228</v>
       </c>
       <c r="C96" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D96" t="s">
         <v>14</v>
@@ -10054,10 +10185,10 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B97" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="C97" t="s">
         <v>292</v>
@@ -10077,22 +10208,22 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B98" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="C98" t="s">
         <v>292</v>
       </c>
       <c r="D98" t="s">
-        <v>14</v>
+        <v>225</v>
       </c>
       <c r="E98" t="s">
-        <v>14</v>
+        <v>225</v>
       </c>
       <c r="F98" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="G98">
         <v>1</v>
@@ -10100,22 +10231,22 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B99" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C99" t="s">
         <v>292</v>
       </c>
       <c r="D99" t="s">
-        <v>14</v>
+        <v>225</v>
       </c>
       <c r="E99" t="s">
-        <v>14</v>
+        <v>225</v>
       </c>
       <c r="F99" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="G99">
         <v>1</v>
@@ -10123,22 +10254,22 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>201</v>
+        <v>118</v>
       </c>
       <c r="B100" t="s">
-        <v>40</v>
+        <v>227</v>
       </c>
       <c r="C100" t="s">
         <v>292</v>
       </c>
       <c r="D100" t="s">
-        <v>14</v>
+        <v>225</v>
       </c>
       <c r="E100" t="s">
-        <v>14</v>
+        <v>225</v>
       </c>
       <c r="F100" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="G100">
         <v>1</v>
@@ -10146,22 +10277,22 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>5</v>
+        <v>118</v>
       </c>
       <c r="B101" t="s">
-        <v>88</v>
+        <v>228</v>
       </c>
       <c r="C101" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D101" t="s">
-        <v>14</v>
+        <v>225</v>
       </c>
       <c r="E101" t="s">
-        <v>14</v>
+        <v>225</v>
       </c>
       <c r="F101" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="G101">
         <v>1</v>
@@ -10169,22 +10300,22 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>5</v>
+        <v>118</v>
       </c>
       <c r="B102" t="s">
-        <v>69</v>
+        <v>193</v>
       </c>
       <c r="C102" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D102" t="s">
-        <v>14</v>
+        <v>225</v>
       </c>
       <c r="E102" t="s">
-        <v>14</v>
+        <v>225</v>
       </c>
       <c r="F102" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="G102">
         <v>1</v>
@@ -10192,13 +10323,13 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="B103" t="s">
-        <v>22</v>
+        <v>205</v>
       </c>
       <c r="C103" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D103" t="s">
         <v>14</v>
@@ -10215,10 +10346,10 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="B104" t="s">
-        <v>273</v>
+        <v>203</v>
       </c>
       <c r="C104" t="s">
         <v>293</v>
@@ -10238,13 +10369,13 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="B105" t="s">
-        <v>272</v>
+        <v>192</v>
       </c>
       <c r="C105" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D105" t="s">
         <v>14</v>
@@ -10261,13 +10392,13 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="B106" t="s">
-        <v>175</v>
+        <v>204</v>
       </c>
       <c r="C106" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D106" t="s">
         <v>14</v>
@@ -10284,10 +10415,10 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="B107" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="C107" t="s">
         <v>292</v>
@@ -10307,13 +10438,13 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="B108" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="C108" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D108" t="s">
         <v>14</v>
@@ -10330,10 +10461,10 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="B109" t="s">
-        <v>275</v>
+        <v>230</v>
       </c>
       <c r="C109" t="s">
         <v>296</v>
@@ -10353,10 +10484,10 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="B110" t="s">
-        <v>227</v>
+        <v>206</v>
       </c>
       <c r="C110" t="s">
         <v>292</v>
@@ -10371,15 +10502,15 @@
         <v>302</v>
       </c>
       <c r="G110">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="B111" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="C111" t="s">
         <v>292</v>
@@ -10399,10 +10530,10 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="B112" t="s">
-        <v>276</v>
+        <v>231</v>
       </c>
       <c r="C112" t="s">
         <v>292</v>
@@ -10422,13 +10553,13 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="B113" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C113" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="D113" t="s">
         <v>14</v>
@@ -10445,7 +10576,7 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="B114" t="s">
         <v>193</v>
@@ -10468,10 +10599,10 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="B115" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C115" t="s">
         <v>293</v>
@@ -10491,10 +10622,10 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>109</v>
+        <v>288</v>
       </c>
       <c r="B116" t="s">
-        <v>17</v>
+        <v>88</v>
       </c>
       <c r="C116" t="s">
         <v>293</v>
@@ -10514,19 +10645,19 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>109</v>
+        <v>288</v>
       </c>
       <c r="B117" t="s">
-        <v>204</v>
+        <v>88</v>
       </c>
       <c r="C117" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D117" t="s">
-        <v>14</v>
+        <v>278</v>
       </c>
       <c r="E117" t="s">
-        <v>14</v>
+        <v>278</v>
       </c>
       <c r="F117" t="s">
         <v>302</v>
@@ -10537,19 +10668,19 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>109</v>
+        <v>288</v>
       </c>
       <c r="B118" t="s">
-        <v>207</v>
+        <v>88</v>
       </c>
       <c r="C118" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D118" t="s">
-        <v>14</v>
+        <v>287</v>
       </c>
       <c r="E118" t="s">
-        <v>14</v>
+        <v>287</v>
       </c>
       <c r="F118" t="s">
         <v>302</v>
@@ -10560,13 +10691,13 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>109</v>
+        <v>288</v>
       </c>
       <c r="B119" t="s">
-        <v>193</v>
+        <v>236</v>
       </c>
       <c r="C119" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D119" t="s">
         <v>14</v>
@@ -10583,13 +10714,13 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>109</v>
+        <v>288</v>
       </c>
       <c r="B120" t="s">
-        <v>277</v>
+        <v>113</v>
       </c>
       <c r="C120" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D120" t="s">
         <v>14</v>
@@ -10606,10 +10737,10 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>45</v>
+        <v>288</v>
       </c>
       <c r="B121" t="s">
-        <v>205</v>
+        <v>235</v>
       </c>
       <c r="C121" t="s">
         <v>292</v>
@@ -10629,13 +10760,13 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>45</v>
+        <v>288</v>
       </c>
       <c r="B122" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="C122" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="D122" t="s">
         <v>14</v>
@@ -10652,13 +10783,13 @@
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>45</v>
+        <v>288</v>
       </c>
       <c r="B123" t="s">
-        <v>157</v>
+        <v>43</v>
       </c>
       <c r="C123" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D123" t="s">
         <v>14</v>
@@ -10675,13 +10806,13 @@
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>45</v>
+        <v>288</v>
       </c>
       <c r="B124" t="s">
-        <v>284</v>
+        <v>230</v>
       </c>
       <c r="C124" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D124" t="s">
         <v>14</v>
@@ -10698,10 +10829,10 @@
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>45</v>
+        <v>288</v>
       </c>
       <c r="B125" t="s">
-        <v>286</v>
+        <v>193</v>
       </c>
       <c r="C125" t="s">
         <v>292</v>
@@ -10721,22 +10852,22 @@
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>45</v>
+        <v>288</v>
       </c>
       <c r="B126" t="s">
-        <v>204</v>
+        <v>236</v>
       </c>
       <c r="C126" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D126" t="s">
-        <v>14</v>
+        <v>134</v>
       </c>
       <c r="E126" t="s">
-        <v>14</v>
+        <v>134</v>
       </c>
       <c r="F126" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G126">
         <v>1</v>
@@ -10744,22 +10875,22 @@
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>45</v>
+        <v>288</v>
       </c>
       <c r="B127" t="s">
-        <v>282</v>
+        <v>113</v>
       </c>
       <c r="C127" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D127" t="s">
-        <v>14</v>
+        <v>134</v>
       </c>
       <c r="E127" t="s">
-        <v>14</v>
+        <v>134</v>
       </c>
       <c r="F127" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G127">
         <v>1</v>
@@ -10767,22 +10898,22 @@
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>45</v>
+        <v>288</v>
       </c>
       <c r="B128" t="s">
-        <v>280</v>
+        <v>235</v>
       </c>
       <c r="C128" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D128" t="s">
-        <v>14</v>
+        <v>134</v>
       </c>
       <c r="E128" t="s">
-        <v>14</v>
+        <v>134</v>
       </c>
       <c r="F128" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G128">
         <v>1</v>
@@ -10790,22 +10921,22 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>45</v>
+        <v>288</v>
       </c>
       <c r="B129" t="s">
-        <v>283</v>
+        <v>220</v>
       </c>
       <c r="C129" t="s">
         <v>292</v>
       </c>
       <c r="D129" t="s">
-        <v>14</v>
+        <v>134</v>
       </c>
       <c r="E129" t="s">
-        <v>14</v>
+        <v>134</v>
       </c>
       <c r="F129" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G129">
         <v>1</v>
@@ -10813,22 +10944,22 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>45</v>
+        <v>288</v>
       </c>
       <c r="B130" t="s">
-        <v>40</v>
+        <v>230</v>
       </c>
       <c r="C130" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D130" t="s">
-        <v>14</v>
+        <v>134</v>
       </c>
       <c r="E130" t="s">
-        <v>14</v>
+        <v>134</v>
       </c>
       <c r="F130" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G130">
         <v>1</v>
@@ -10836,22 +10967,22 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>45</v>
+        <v>288</v>
       </c>
       <c r="B131" t="s">
-        <v>279</v>
+        <v>193</v>
       </c>
       <c r="C131" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="D131" t="s">
-        <v>14</v>
+        <v>134</v>
       </c>
       <c r="E131" t="s">
-        <v>14</v>
+        <v>134</v>
       </c>
       <c r="F131" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G131">
         <v>1</v>
@@ -10859,22 +10990,22 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>45</v>
+        <v>288</v>
       </c>
       <c r="B132" t="s">
-        <v>276</v>
+        <v>113</v>
       </c>
       <c r="C132" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D132" t="s">
-        <v>14</v>
+        <v>162</v>
       </c>
       <c r="E132" t="s">
-        <v>14</v>
+        <v>162</v>
       </c>
       <c r="F132" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G132">
         <v>1</v>
@@ -10882,13 +11013,13 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="B133" t="s">
-        <v>230</v>
+        <v>205</v>
       </c>
       <c r="C133" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="D133" t="s">
         <v>14</v>
@@ -10905,13 +11036,13 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="B134" t="s">
-        <v>285</v>
+        <v>203</v>
       </c>
       <c r="C134" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D134" t="s">
         <v>14</v>
@@ -10928,10 +11059,10 @@
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="B135" t="s">
-        <v>281</v>
+        <v>91</v>
       </c>
       <c r="C135" t="s">
         <v>292</v>
@@ -10951,10 +11082,10 @@
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>198</v>
+        <v>33</v>
       </c>
       <c r="B136" t="s">
-        <v>169</v>
+        <v>204</v>
       </c>
       <c r="C136" t="s">
         <v>292</v>
@@ -10974,13 +11105,13 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>148</v>
+        <v>33</v>
       </c>
       <c r="B137" t="s">
-        <v>88</v>
+        <v>207</v>
       </c>
       <c r="C137" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D137" t="s">
         <v>14</v>
@@ -10997,13 +11128,13 @@
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>148</v>
+        <v>33</v>
       </c>
       <c r="B138" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="C138" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D138" t="s">
         <v>14</v>
@@ -11020,16 +11151,16 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="B139" t="s">
-        <v>52</v>
+        <v>206</v>
       </c>
       <c r="C139" t="s">
         <v>292</v>
       </c>
       <c r="D139" t="s">
-        <v>244</v>
+        <v>14</v>
       </c>
       <c r="E139" t="s">
         <v>14</v>
@@ -11043,19 +11174,19 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="B140" t="s">
-        <v>55</v>
+        <v>220</v>
       </c>
       <c r="C140" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="D140" t="s">
-        <v>252</v>
+        <v>130</v>
       </c>
       <c r="E140" t="s">
-        <v>14</v>
+        <v>130</v>
       </c>
       <c r="F140" t="s">
         <v>302</v>
@@ -11066,19 +11197,19 @@
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>213</v>
+        <v>33</v>
       </c>
       <c r="B141" t="s">
-        <v>69</v>
+        <v>239</v>
       </c>
       <c r="C141" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D141" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="E141" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="F141" t="s">
         <v>302</v>
@@ -11089,19 +11220,19 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>80</v>
+        <v>33</v>
       </c>
       <c r="B142" t="s">
-        <v>81</v>
+        <v>240</v>
       </c>
       <c r="C142" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D142" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="E142" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="F142" t="s">
         <v>302</v>
@@ -11112,19 +11243,19 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>132</v>
+        <v>33</v>
       </c>
       <c r="B143" t="s">
-        <v>73</v>
+        <v>238</v>
       </c>
       <c r="C143" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D143" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="E143" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="F143" t="s">
         <v>302</v>
@@ -11135,19 +11266,19 @@
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>144</v>
+        <v>33</v>
       </c>
       <c r="B144" t="s">
-        <v>73</v>
+        <v>237</v>
       </c>
       <c r="C144" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D144" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="E144" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="F144" t="s">
         <v>302</v>
@@ -11158,22 +11289,22 @@
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>199</v>
+        <v>33</v>
       </c>
       <c r="B145" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="C145" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D145" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="E145" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="F145" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G145">
         <v>1</v>
@@ -11181,19 +11312,19 @@
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>60</v>
+        <v>164</v>
       </c>
       <c r="B146" t="s">
-        <v>84</v>
+        <v>242</v>
       </c>
       <c r="C146" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D146" t="s">
-        <v>124</v>
+        <v>14</v>
       </c>
       <c r="E146" t="s">
-        <v>124</v>
+        <v>14</v>
       </c>
       <c r="F146" t="s">
         <v>302</v>
@@ -11204,19 +11335,19 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>60</v>
+        <v>164</v>
       </c>
       <c r="B147" t="s">
-        <v>218</v>
+        <v>25</v>
       </c>
       <c r="C147" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D147" t="s">
-        <v>124</v>
+        <v>14</v>
       </c>
       <c r="E147" t="s">
-        <v>124</v>
+        <v>14</v>
       </c>
       <c r="F147" t="s">
         <v>302</v>
@@ -11227,19 +11358,19 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>60</v>
+        <v>164</v>
       </c>
       <c r="B148" t="s">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="C148" t="s">
         <v>292</v>
       </c>
       <c r="D148" t="s">
-        <v>124</v>
+        <v>14</v>
       </c>
       <c r="E148" t="s">
-        <v>124</v>
+        <v>14</v>
       </c>
       <c r="F148" t="s">
         <v>302</v>
@@ -11250,22 +11381,22 @@
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>60</v>
+        <v>164</v>
       </c>
       <c r="B149" t="s">
-        <v>220</v>
+        <v>242</v>
       </c>
       <c r="C149" t="s">
         <v>292</v>
       </c>
       <c r="D149" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="E149" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="F149" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G149">
         <v>1</v>
@@ -11273,22 +11404,22 @@
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>60</v>
+        <v>164</v>
       </c>
       <c r="B150" t="s">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="C150" t="s">
         <v>292</v>
       </c>
       <c r="D150" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="E150" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="F150" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G150">
         <v>1</v>
@@ -11296,22 +11427,22 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>64</v>
+        <v>164</v>
       </c>
       <c r="B151" t="s">
-        <v>65</v>
+        <v>242</v>
       </c>
       <c r="C151" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D151" t="s">
-        <v>124</v>
+        <v>162</v>
       </c>
       <c r="E151" t="s">
-        <v>124</v>
+        <v>162</v>
       </c>
       <c r="F151" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G151">
         <v>1</v>
@@ -11319,22 +11450,22 @@
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>105</v>
+        <v>164</v>
       </c>
       <c r="B152" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="C152" t="s">
         <v>292</v>
       </c>
       <c r="D152" t="s">
-        <v>124</v>
+        <v>162</v>
       </c>
       <c r="E152" t="s">
-        <v>124</v>
+        <v>162</v>
       </c>
       <c r="F152" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G152">
         <v>1</v>
@@ -11342,19 +11473,19 @@
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>105</v>
+        <v>51</v>
       </c>
       <c r="B153" t="s">
-        <v>247</v>
+        <v>52</v>
       </c>
       <c r="C153" t="s">
         <v>292</v>
       </c>
       <c r="D153" t="s">
-        <v>124</v>
+        <v>244</v>
       </c>
       <c r="E153" t="s">
-        <v>124</v>
+        <v>14</v>
       </c>
       <c r="F153" t="s">
         <v>302</v>
@@ -11365,19 +11496,19 @@
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>105</v>
+        <v>308</v>
       </c>
       <c r="B154" t="s">
-        <v>250</v>
+        <v>205</v>
       </c>
       <c r="C154" t="s">
         <v>292</v>
       </c>
       <c r="D154" t="s">
-        <v>124</v>
+        <v>14</v>
       </c>
       <c r="E154" t="s">
-        <v>124</v>
+        <v>14</v>
       </c>
       <c r="F154" t="s">
         <v>302</v>
@@ -11388,19 +11519,19 @@
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>105</v>
+        <v>308</v>
       </c>
       <c r="B155" t="s">
-        <v>220</v>
+        <v>203</v>
       </c>
       <c r="C155" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D155" t="s">
-        <v>124</v>
+        <v>14</v>
       </c>
       <c r="E155" t="s">
-        <v>124</v>
+        <v>14</v>
       </c>
       <c r="F155" t="s">
         <v>302</v>
@@ -11411,19 +11542,19 @@
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>105</v>
+        <v>308</v>
       </c>
       <c r="B156" t="s">
-        <v>227</v>
+        <v>204</v>
       </c>
       <c r="C156" t="s">
         <v>292</v>
       </c>
       <c r="D156" t="s">
-        <v>124</v>
+        <v>14</v>
       </c>
       <c r="E156" t="s">
-        <v>124</v>
+        <v>14</v>
       </c>
       <c r="F156" t="s">
         <v>302</v>
@@ -11434,19 +11565,19 @@
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>105</v>
+        <v>308</v>
       </c>
       <c r="B157" t="s">
-        <v>249</v>
+        <v>207</v>
       </c>
       <c r="C157" t="s">
         <v>292</v>
       </c>
       <c r="D157" t="s">
-        <v>124</v>
+        <v>14</v>
       </c>
       <c r="E157" t="s">
-        <v>124</v>
+        <v>14</v>
       </c>
       <c r="F157" t="s">
         <v>302</v>
@@ -11457,19 +11588,19 @@
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>105</v>
+        <v>308</v>
       </c>
       <c r="B158" t="s">
-        <v>246</v>
+        <v>206</v>
       </c>
       <c r="C158" t="s">
         <v>292</v>
       </c>
       <c r="D158" t="s">
-        <v>124</v>
+        <v>14</v>
       </c>
       <c r="E158" t="s">
-        <v>124</v>
+        <v>14</v>
       </c>
       <c r="F158" t="s">
         <v>302</v>
@@ -11480,19 +11611,19 @@
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="B159" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="C159" t="s">
         <v>293</v>
       </c>
       <c r="D159" t="s">
-        <v>124</v>
+        <v>14</v>
       </c>
       <c r="E159" t="s">
-        <v>124</v>
+        <v>14</v>
       </c>
       <c r="F159" t="s">
         <v>302</v>
@@ -11503,19 +11634,19 @@
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="B160" t="s">
-        <v>253</v>
+        <v>116</v>
       </c>
       <c r="C160" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D160" t="s">
-        <v>124</v>
+        <v>14</v>
       </c>
       <c r="E160" t="s">
-        <v>124</v>
+        <v>14</v>
       </c>
       <c r="F160" t="s">
         <v>302</v>
@@ -11526,10 +11657,10 @@
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="B161" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="C161" t="s">
         <v>292</v>
@@ -11549,13 +11680,13 @@
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>5</v>
+        <v>105</v>
       </c>
       <c r="B162" t="s">
-        <v>69</v>
+        <v>247</v>
       </c>
       <c r="C162" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D162" t="s">
         <v>124</v>
@@ -11572,10 +11703,10 @@
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>5</v>
+        <v>105</v>
       </c>
       <c r="B163" t="s">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="C163" t="s">
         <v>292</v>
@@ -11595,10 +11726,10 @@
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>5</v>
+        <v>105</v>
       </c>
       <c r="B164" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="C164" t="s">
         <v>292</v>
@@ -11618,10 +11749,10 @@
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>5</v>
+        <v>105</v>
       </c>
       <c r="B165" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="C165" t="s">
         <v>292</v>
@@ -11641,13 +11772,13 @@
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>148</v>
+        <v>105</v>
       </c>
       <c r="B166" t="s">
-        <v>69</v>
+        <v>249</v>
       </c>
       <c r="C166" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D166" t="s">
         <v>124</v>
@@ -11664,19 +11795,19 @@
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>33</v>
+        <v>105</v>
       </c>
       <c r="B167" t="s">
-        <v>220</v>
+        <v>246</v>
       </c>
       <c r="C167" t="s">
         <v>292</v>
       </c>
       <c r="D167" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E167" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="F167" t="s">
         <v>302</v>
@@ -11687,22 +11818,22 @@
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>33</v>
+        <v>105</v>
       </c>
       <c r="B168" t="s">
-        <v>239</v>
+        <v>116</v>
       </c>
       <c r="C168" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D168" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E168" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F168" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G168">
         <v>1</v>
@@ -11710,22 +11841,22 @@
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>33</v>
+        <v>105</v>
       </c>
       <c r="B169" t="s">
-        <v>240</v>
+        <v>106</v>
       </c>
       <c r="C169" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D169" t="s">
-        <v>130</v>
+        <v>245</v>
       </c>
       <c r="E169" t="s">
-        <v>130</v>
+        <v>245</v>
       </c>
       <c r="F169" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G169">
         <v>1</v>
@@ -11733,22 +11864,22 @@
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>33</v>
+        <v>105</v>
       </c>
       <c r="B170" t="s">
-        <v>238</v>
+        <v>116</v>
       </c>
       <c r="C170" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D170" t="s">
-        <v>130</v>
+        <v>162</v>
       </c>
       <c r="E170" t="s">
-        <v>130</v>
+        <v>162</v>
       </c>
       <c r="F170" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G170">
         <v>1</v>
@@ -11756,19 +11887,19 @@
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>33</v>
+        <v>105</v>
       </c>
       <c r="B171" t="s">
-        <v>237</v>
+        <v>78</v>
       </c>
       <c r="C171" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D171" t="s">
-        <v>130</v>
+        <v>14</v>
       </c>
       <c r="E171" t="s">
-        <v>130</v>
+        <v>14</v>
       </c>
       <c r="F171" t="s">
         <v>302</v>
@@ -11779,19 +11910,19 @@
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="B172" t="s">
-        <v>220</v>
+        <v>78</v>
       </c>
       <c r="C172" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D172" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E172" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="F172" t="s">
         <v>302</v>
@@ -11802,22 +11933,22 @@
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="B173" t="s">
-        <v>239</v>
+        <v>78</v>
       </c>
       <c r="C173" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D173" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E173" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F173" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G173">
         <v>1</v>
@@ -11825,19 +11956,19 @@
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="B174" t="s">
-        <v>240</v>
+        <v>55</v>
       </c>
       <c r="C174" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D174" t="s">
-        <v>130</v>
+        <v>252</v>
       </c>
       <c r="E174" t="s">
-        <v>130</v>
+        <v>14</v>
       </c>
       <c r="F174" t="s">
         <v>302</v>
@@ -11848,10 +11979,10 @@
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="B175" t="s">
-        <v>238</v>
+        <v>220</v>
       </c>
       <c r="C175" t="s">
         <v>292</v>
@@ -11871,10 +12002,10 @@
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="B176" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C176" t="s">
         <v>292</v>
@@ -11894,10 +12025,10 @@
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>241</v>
+        <v>105</v>
       </c>
       <c r="B177" t="s">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="C177" t="s">
         <v>292</v>
@@ -11917,10 +12048,10 @@
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>241</v>
+        <v>105</v>
       </c>
       <c r="B178" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C178" t="s">
         <v>292</v>
@@ -11940,10 +12071,10 @@
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>241</v>
+        <v>105</v>
       </c>
       <c r="B179" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C179" t="s">
         <v>292</v>
@@ -11963,19 +12094,19 @@
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>241</v>
+        <v>94</v>
       </c>
       <c r="B180" t="s">
-        <v>238</v>
+        <v>95</v>
       </c>
       <c r="C180" t="s">
         <v>292</v>
       </c>
       <c r="D180" t="s">
-        <v>130</v>
+        <v>14</v>
       </c>
       <c r="E180" t="s">
-        <v>130</v>
+        <v>14</v>
       </c>
       <c r="F180" t="s">
         <v>302</v>
@@ -11986,22 +12117,22 @@
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>241</v>
+        <v>94</v>
       </c>
       <c r="B181" t="s">
-        <v>237</v>
+        <v>95</v>
       </c>
       <c r="C181" t="s">
         <v>292</v>
       </c>
       <c r="D181" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E181" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F181" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G181">
         <v>1</v>
@@ -12009,19 +12140,19 @@
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>60</v>
+        <v>196</v>
       </c>
       <c r="B182" t="s">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c r="C182" t="s">
         <v>293</v>
       </c>
       <c r="D182" t="s">
-        <v>278</v>
+        <v>14</v>
       </c>
       <c r="E182" t="s">
-        <v>278</v>
+        <v>14</v>
       </c>
       <c r="F182" t="s">
         <v>302</v>
@@ -12032,19 +12163,19 @@
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>288</v>
+        <v>196</v>
       </c>
       <c r="B183" t="s">
-        <v>88</v>
+        <v>169</v>
       </c>
       <c r="C183" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D183" t="s">
-        <v>278</v>
+        <v>14</v>
       </c>
       <c r="E183" t="s">
-        <v>278</v>
+        <v>14</v>
       </c>
       <c r="F183" t="s">
         <v>302</v>
@@ -12055,22 +12186,22 @@
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>5</v>
+        <v>196</v>
       </c>
       <c r="B184" t="s">
-        <v>88</v>
+        <v>169</v>
       </c>
       <c r="C184" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D184" t="s">
-        <v>278</v>
+        <v>134</v>
       </c>
       <c r="E184" t="s">
-        <v>278</v>
+        <v>134</v>
       </c>
       <c r="F184" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G184">
         <v>1</v>
@@ -12078,19 +12209,19 @@
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>109</v>
+        <v>196</v>
       </c>
       <c r="B185" t="s">
-        <v>204</v>
+        <v>169</v>
       </c>
       <c r="C185" t="s">
         <v>292</v>
       </c>
       <c r="D185" t="s">
-        <v>278</v>
+        <v>194</v>
       </c>
       <c r="E185" t="s">
-        <v>278</v>
+        <v>194</v>
       </c>
       <c r="F185" t="s">
         <v>302</v>
@@ -12101,22 +12232,22 @@
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>109</v>
+        <v>196</v>
       </c>
       <c r="B186" t="s">
-        <v>207</v>
+        <v>169</v>
       </c>
       <c r="C186" t="s">
         <v>292</v>
       </c>
       <c r="D186" t="s">
-        <v>278</v>
+        <v>162</v>
       </c>
       <c r="E186" t="s">
-        <v>278</v>
+        <v>162</v>
       </c>
       <c r="F186" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G186">
         <v>1</v>
@@ -12124,19 +12255,19 @@
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>109</v>
+        <v>197</v>
       </c>
       <c r="B187" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="C187" t="s">
         <v>292</v>
       </c>
       <c r="D187" t="s">
-        <v>278</v>
+        <v>14</v>
       </c>
       <c r="E187" t="s">
-        <v>278</v>
+        <v>14</v>
       </c>
       <c r="F187" t="s">
         <v>302</v>
@@ -12147,22 +12278,22 @@
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>109</v>
+        <v>197</v>
       </c>
       <c r="B188" t="s">
-        <v>277</v>
+        <v>169</v>
       </c>
       <c r="C188" t="s">
         <v>292</v>
       </c>
       <c r="D188" t="s">
-        <v>278</v>
+        <v>134</v>
       </c>
       <c r="E188" t="s">
-        <v>278</v>
+        <v>134</v>
       </c>
       <c r="F188" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G188">
         <v>1</v>
@@ -12170,19 +12301,19 @@
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>45</v>
+        <v>197</v>
       </c>
       <c r="B189" t="s">
-        <v>286</v>
+        <v>169</v>
       </c>
       <c r="C189" t="s">
         <v>292</v>
       </c>
       <c r="D189" t="s">
-        <v>278</v>
+        <v>194</v>
       </c>
       <c r="E189" t="s">
-        <v>278</v>
+        <v>194</v>
       </c>
       <c r="F189" t="s">
         <v>302</v>
@@ -12193,22 +12324,22 @@
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>45</v>
+        <v>197</v>
       </c>
       <c r="B190" t="s">
-        <v>285</v>
+        <v>169</v>
       </c>
       <c r="C190" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="D190" t="s">
-        <v>278</v>
+        <v>162</v>
       </c>
       <c r="E190" t="s">
-        <v>278</v>
+        <v>162</v>
       </c>
       <c r="F190" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G190">
         <v>1</v>
@@ -12216,19 +12347,19 @@
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>148</v>
+        <v>122</v>
       </c>
       <c r="B191" t="s">
-        <v>88</v>
+        <v>205</v>
       </c>
       <c r="C191" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D191" t="s">
-        <v>278</v>
+        <v>14</v>
       </c>
       <c r="E191" t="s">
-        <v>278</v>
+        <v>14</v>
       </c>
       <c r="F191" t="s">
         <v>302</v>
@@ -12239,45 +12370,45 @@
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>152</v>
+        <v>122</v>
       </c>
       <c r="B192" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="C192" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D192" t="s">
-        <v>134</v>
+        <v>14</v>
       </c>
       <c r="E192" t="s">
-        <v>134</v>
+        <v>14</v>
       </c>
       <c r="F192" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G192">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>152</v>
+        <v>122</v>
       </c>
       <c r="B193" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C193" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D193" t="s">
-        <v>134</v>
+        <v>14</v>
       </c>
       <c r="E193" t="s">
-        <v>134</v>
+        <v>14</v>
       </c>
       <c r="F193" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G193">
         <v>1</v>
@@ -12285,22 +12416,22 @@
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>152</v>
+        <v>122</v>
       </c>
       <c r="B194" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="C194" t="s">
         <v>292</v>
       </c>
       <c r="D194" t="s">
-        <v>134</v>
+        <v>14</v>
       </c>
       <c r="E194" t="s">
-        <v>134</v>
+        <v>14</v>
       </c>
       <c r="F194" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G194">
         <v>1</v>
@@ -12308,45 +12439,45 @@
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>152</v>
+        <v>122</v>
       </c>
       <c r="B195" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="C195" t="s">
         <v>292</v>
       </c>
       <c r="D195" t="s">
-        <v>134</v>
+        <v>14</v>
       </c>
       <c r="E195" t="s">
-        <v>134</v>
+        <v>14</v>
       </c>
       <c r="F195" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G195">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>152</v>
+        <v>122</v>
       </c>
       <c r="B196" t="s">
-        <v>169</v>
+        <v>253</v>
       </c>
       <c r="C196" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D196" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="E196" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="F196" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G196">
         <v>1</v>
@@ -12354,22 +12485,22 @@
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>152</v>
+        <v>122</v>
       </c>
       <c r="B197" t="s">
-        <v>193</v>
+        <v>254</v>
       </c>
       <c r="C197" t="s">
         <v>292</v>
       </c>
       <c r="D197" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="E197" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="F197" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G197">
         <v>1</v>
@@ -12377,22 +12508,22 @@
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B198" t="s">
-        <v>169</v>
+        <v>40</v>
       </c>
       <c r="C198" t="s">
         <v>292</v>
       </c>
       <c r="D198" t="s">
-        <v>134</v>
+        <v>14</v>
       </c>
       <c r="E198" t="s">
-        <v>134</v>
+        <v>14</v>
       </c>
       <c r="F198" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G198">
         <v>1</v>
@@ -12400,13 +12531,13 @@
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="B199" t="s">
-        <v>69</v>
+        <v>192</v>
       </c>
       <c r="C199" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D199" t="s">
         <v>134</v>
@@ -12423,13 +12554,13 @@
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>132</v>
+        <v>201</v>
       </c>
       <c r="B200" t="s">
-        <v>133</v>
+        <v>202</v>
       </c>
       <c r="C200" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D200" t="s">
         <v>134</v>
@@ -12446,13 +12577,13 @@
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>132</v>
+        <v>201</v>
       </c>
       <c r="B201" t="s">
-        <v>73</v>
+        <v>191</v>
       </c>
       <c r="C201" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D201" t="s">
         <v>134</v>
@@ -12469,19 +12600,19 @@
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>144</v>
+        <v>201</v>
       </c>
       <c r="B202" t="s">
-        <v>73</v>
+        <v>179</v>
       </c>
       <c r="C202" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D202" t="s">
-        <v>134</v>
+        <v>256</v>
       </c>
       <c r="E202" t="s">
-        <v>134</v>
+        <v>261</v>
       </c>
       <c r="F202" t="s">
         <v>303</v>
@@ -12492,19 +12623,19 @@
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>144</v>
+        <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>145</v>
+        <v>262</v>
       </c>
       <c r="C203" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D203" t="s">
-        <v>134</v>
+        <v>261</v>
       </c>
       <c r="E203" t="s">
-        <v>134</v>
+        <v>261</v>
       </c>
       <c r="F203" t="s">
         <v>303</v>
@@ -12515,19 +12646,19 @@
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B204" t="s">
-        <v>69</v>
+        <v>260</v>
       </c>
       <c r="C204" t="s">
         <v>293</v>
       </c>
       <c r="D204" t="s">
-        <v>134</v>
+        <v>261</v>
       </c>
       <c r="E204" t="s">
-        <v>134</v>
+        <v>261</v>
       </c>
       <c r="F204" t="s">
         <v>303</v>
@@ -12538,19 +12669,19 @@
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B205" t="s">
-        <v>192</v>
+        <v>263</v>
       </c>
       <c r="C205" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="D205" t="s">
-        <v>134</v>
+        <v>261</v>
       </c>
       <c r="E205" t="s">
-        <v>134</v>
+        <v>261</v>
       </c>
       <c r="F205" t="s">
         <v>303</v>
@@ -12561,19 +12692,19 @@
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B206" t="s">
-        <v>202</v>
+        <v>258</v>
       </c>
       <c r="C206" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D206" t="s">
-        <v>134</v>
+        <v>261</v>
       </c>
       <c r="E206" t="s">
-        <v>134</v>
+        <v>261</v>
       </c>
       <c r="F206" t="s">
         <v>303</v>
@@ -12584,19 +12715,19 @@
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B207" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="C207" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="D207" t="s">
-        <v>134</v>
+        <v>162</v>
       </c>
       <c r="E207" t="s">
-        <v>134</v>
+        <v>162</v>
       </c>
       <c r="F207" t="s">
         <v>303</v>
@@ -12607,19 +12738,19 @@
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B208" t="s">
-        <v>192</v>
+        <v>262</v>
       </c>
       <c r="C208" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="D208" t="s">
-        <v>134</v>
+        <v>162</v>
       </c>
       <c r="E208" t="s">
-        <v>134</v>
+        <v>162</v>
       </c>
       <c r="F208" t="s">
         <v>303</v>
@@ -12630,19 +12761,19 @@
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B209" t="s">
-        <v>202</v>
+        <v>260</v>
       </c>
       <c r="C209" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D209" t="s">
-        <v>134</v>
+        <v>162</v>
       </c>
       <c r="E209" t="s">
-        <v>134</v>
+        <v>162</v>
       </c>
       <c r="F209" t="s">
         <v>303</v>
@@ -12653,19 +12784,19 @@
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B210" t="s">
-        <v>191</v>
+        <v>263</v>
       </c>
       <c r="C210" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="D210" t="s">
-        <v>134</v>
+        <v>162</v>
       </c>
       <c r="E210" t="s">
-        <v>134</v>
+        <v>162</v>
       </c>
       <c r="F210" t="s">
         <v>303</v>
@@ -12676,19 +12807,19 @@
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>42</v>
+        <v>201</v>
       </c>
       <c r="B211" t="s">
-        <v>236</v>
+        <v>258</v>
       </c>
       <c r="C211" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D211" t="s">
-        <v>134</v>
+        <v>162</v>
       </c>
       <c r="E211" t="s">
-        <v>134</v>
+        <v>162</v>
       </c>
       <c r="F211" t="s">
         <v>303</v>
@@ -12699,19 +12830,19 @@
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>42</v>
+        <v>201</v>
       </c>
       <c r="B212" t="s">
-        <v>113</v>
+        <v>255</v>
       </c>
       <c r="C212" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D212" t="s">
-        <v>134</v>
+        <v>256</v>
       </c>
       <c r="E212" t="s">
-        <v>134</v>
+        <v>261</v>
       </c>
       <c r="F212" t="s">
         <v>303</v>
@@ -12722,19 +12853,19 @@
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>42</v>
+        <v>201</v>
       </c>
       <c r="B213" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="C213" t="s">
         <v>292</v>
       </c>
       <c r="D213" t="s">
-        <v>134</v>
+        <v>256</v>
       </c>
       <c r="E213" t="s">
-        <v>134</v>
+        <v>261</v>
       </c>
       <c r="F213" t="s">
         <v>303</v>
@@ -12745,19 +12876,19 @@
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>42</v>
+        <v>201</v>
       </c>
       <c r="B214" t="s">
-        <v>220</v>
+        <v>258</v>
       </c>
       <c r="C214" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="D214" t="s">
-        <v>134</v>
+        <v>256</v>
       </c>
       <c r="E214" t="s">
-        <v>134</v>
+        <v>261</v>
       </c>
       <c r="F214" t="s">
         <v>303</v>
@@ -12768,19 +12899,19 @@
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>42</v>
+        <v>201</v>
       </c>
       <c r="B215" t="s">
-        <v>230</v>
+        <v>257</v>
       </c>
       <c r="C215" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D215" t="s">
-        <v>134</v>
+        <v>256</v>
       </c>
       <c r="E215" t="s">
-        <v>134</v>
+        <v>261</v>
       </c>
       <c r="F215" t="s">
         <v>303</v>
@@ -12791,19 +12922,19 @@
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>42</v>
+        <v>201</v>
       </c>
       <c r="B216" t="s">
-        <v>193</v>
+        <v>259</v>
       </c>
       <c r="C216" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="D216" t="s">
-        <v>134</v>
+        <v>256</v>
       </c>
       <c r="E216" t="s">
-        <v>134</v>
+        <v>261</v>
       </c>
       <c r="F216" t="s">
         <v>303</v>
@@ -12814,19 +12945,19 @@
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>33</v>
+        <v>201</v>
       </c>
       <c r="B217" t="s">
-        <v>91</v>
+        <v>255</v>
       </c>
       <c r="C217" t="s">
         <v>292</v>
       </c>
       <c r="D217" t="s">
-        <v>134</v>
+        <v>162</v>
       </c>
       <c r="E217" t="s">
-        <v>134</v>
+        <v>162</v>
       </c>
       <c r="F217" t="s">
         <v>303</v>
@@ -12837,19 +12968,19 @@
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>164</v>
+        <v>201</v>
       </c>
       <c r="B218" t="s">
-        <v>242</v>
+        <v>220</v>
       </c>
       <c r="C218" t="s">
         <v>292</v>
       </c>
       <c r="D218" t="s">
-        <v>134</v>
+        <v>162</v>
       </c>
       <c r="E218" t="s">
-        <v>134</v>
+        <v>162</v>
       </c>
       <c r="F218" t="s">
         <v>303</v>
@@ -12860,19 +12991,19 @@
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>164</v>
+        <v>201</v>
       </c>
       <c r="B219" t="s">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="C219" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="D219" t="s">
-        <v>134</v>
+        <v>162</v>
       </c>
       <c r="E219" t="s">
-        <v>134</v>
+        <v>162</v>
       </c>
       <c r="F219" t="s">
         <v>303</v>
@@ -12883,19 +13014,19 @@
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>105</v>
+        <v>201</v>
       </c>
       <c r="B220" t="s">
-        <v>116</v>
+        <v>257</v>
       </c>
       <c r="C220" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D220" t="s">
-        <v>134</v>
+        <v>162</v>
       </c>
       <c r="E220" t="s">
-        <v>134</v>
+        <v>162</v>
       </c>
       <c r="F220" t="s">
         <v>303</v>
@@ -12906,19 +13037,19 @@
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>94</v>
+        <v>201</v>
       </c>
       <c r="B221" t="s">
-        <v>95</v>
+        <v>259</v>
       </c>
       <c r="C221" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="D221" t="s">
-        <v>134</v>
+        <v>162</v>
       </c>
       <c r="E221" t="s">
-        <v>134</v>
+        <v>162</v>
       </c>
       <c r="F221" t="s">
         <v>303</v>
@@ -12929,22 +13060,22 @@
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>196</v>
+        <v>5</v>
       </c>
       <c r="B222" t="s">
-        <v>169</v>
+        <v>266</v>
       </c>
       <c r="C222" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D222" t="s">
-        <v>134</v>
+        <v>267</v>
       </c>
       <c r="E222" t="s">
-        <v>134</v>
+        <v>267</v>
       </c>
       <c r="F222" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G222">
         <v>1</v>
@@ -12952,22 +13083,22 @@
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>197</v>
+        <v>5</v>
       </c>
       <c r="B223" t="s">
-        <v>169</v>
+        <v>271</v>
       </c>
       <c r="C223" t="s">
         <v>292</v>
       </c>
       <c r="D223" t="s">
-        <v>134</v>
+        <v>267</v>
       </c>
       <c r="E223" t="s">
-        <v>134</v>
+        <v>267</v>
       </c>
       <c r="F223" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G223">
         <v>1</v>
@@ -12975,22 +13106,22 @@
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>77</v>
+        <v>5</v>
       </c>
       <c r="B224" t="s">
-        <v>78</v>
+        <v>269</v>
       </c>
       <c r="C224" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D224" t="s">
-        <v>134</v>
+        <v>267</v>
       </c>
       <c r="E224" t="s">
-        <v>134</v>
+        <v>267</v>
       </c>
       <c r="F224" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G224">
         <v>1</v>
@@ -12998,22 +13129,22 @@
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>201</v>
+        <v>5</v>
       </c>
       <c r="B225" t="s">
-        <v>192</v>
+        <v>270</v>
       </c>
       <c r="C225" t="s">
         <v>292</v>
       </c>
       <c r="D225" t="s">
-        <v>134</v>
+        <v>267</v>
       </c>
       <c r="E225" t="s">
-        <v>134</v>
+        <v>267</v>
       </c>
       <c r="F225" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G225">
         <v>1</v>
@@ -13021,22 +13152,22 @@
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>201</v>
+        <v>5</v>
       </c>
       <c r="B226" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="C226" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D226" t="s">
-        <v>134</v>
+        <v>267</v>
       </c>
       <c r="E226" t="s">
-        <v>134</v>
+        <v>267</v>
       </c>
       <c r="F226" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G226">
         <v>1</v>
@@ -13044,22 +13175,22 @@
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>201</v>
+        <v>5</v>
       </c>
       <c r="B227" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
       <c r="C227" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D227" t="s">
-        <v>134</v>
+        <v>274</v>
       </c>
       <c r="E227" t="s">
-        <v>134</v>
+        <v>274</v>
       </c>
       <c r="F227" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="G227">
         <v>1</v>
@@ -13070,19 +13201,19 @@
         <v>5</v>
       </c>
       <c r="B228" t="s">
-        <v>69</v>
+        <v>221</v>
       </c>
       <c r="C228" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D228" t="s">
-        <v>134</v>
+        <v>274</v>
       </c>
       <c r="E228" t="s">
-        <v>134</v>
+        <v>274</v>
       </c>
       <c r="F228" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="G228">
         <v>1</v>
@@ -13093,19 +13224,19 @@
         <v>5</v>
       </c>
       <c r="B229" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C229" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D229" t="s">
-        <v>134</v>
+        <v>274</v>
       </c>
       <c r="E229" t="s">
-        <v>134</v>
+        <v>274</v>
       </c>
       <c r="F229" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="G229">
         <v>1</v>
@@ -13116,19 +13247,19 @@
         <v>5</v>
       </c>
       <c r="B230" t="s">
-        <v>175</v>
+        <v>276</v>
       </c>
       <c r="C230" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D230" t="s">
-        <v>134</v>
+        <v>274</v>
       </c>
       <c r="E230" t="s">
-        <v>134</v>
+        <v>274</v>
       </c>
       <c r="F230" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="G230">
         <v>1</v>
@@ -13139,19 +13270,19 @@
         <v>5</v>
       </c>
       <c r="B231" t="s">
-        <v>220</v>
+        <v>193</v>
       </c>
       <c r="C231" t="s">
         <v>292</v>
       </c>
       <c r="D231" t="s">
-        <v>134</v>
+        <v>274</v>
       </c>
       <c r="E231" t="s">
-        <v>134</v>
+        <v>274</v>
       </c>
       <c r="F231" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="G231">
         <v>1</v>
@@ -13162,19 +13293,19 @@
         <v>5</v>
       </c>
       <c r="B232" t="s">
-        <v>172</v>
+        <v>9</v>
       </c>
       <c r="C232" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D232" t="s">
-        <v>134</v>
+        <v>10</v>
       </c>
       <c r="E232" t="s">
-        <v>134</v>
+        <v>10</v>
       </c>
       <c r="F232" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G232">
         <v>1</v>
@@ -13185,22 +13316,22 @@
         <v>5</v>
       </c>
       <c r="B233" t="s">
-        <v>227</v>
+        <v>88</v>
       </c>
       <c r="C233" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D233" t="s">
-        <v>134</v>
+        <v>14</v>
       </c>
       <c r="E233" t="s">
-        <v>134</v>
+        <v>14</v>
       </c>
       <c r="F233" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G233">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.25">
@@ -13208,19 +13339,19 @@
         <v>5</v>
       </c>
       <c r="B234" t="s">
-        <v>219</v>
+        <v>69</v>
       </c>
       <c r="C234" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D234" t="s">
-        <v>134</v>
+        <v>14</v>
       </c>
       <c r="E234" t="s">
-        <v>134</v>
+        <v>14</v>
       </c>
       <c r="F234" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G234">
         <v>1</v>
@@ -13231,19 +13362,19 @@
         <v>5</v>
       </c>
       <c r="B235" t="s">
-        <v>230</v>
+        <v>22</v>
       </c>
       <c r="C235" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D235" t="s">
-        <v>134</v>
+        <v>14</v>
       </c>
       <c r="E235" t="s">
-        <v>134</v>
+        <v>14</v>
       </c>
       <c r="F235" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G235">
         <v>1</v>
@@ -13251,22 +13382,22 @@
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>138</v>
+        <v>5</v>
       </c>
       <c r="B236" t="s">
-        <v>139</v>
+        <v>273</v>
       </c>
       <c r="C236" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D236" t="s">
-        <v>134</v>
+        <v>14</v>
       </c>
       <c r="E236" t="s">
-        <v>134</v>
+        <v>14</v>
       </c>
       <c r="F236" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G236">
         <v>1</v>
@@ -13274,22 +13405,22 @@
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="B237" t="s">
-        <v>205</v>
+        <v>272</v>
       </c>
       <c r="C237" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D237" t="s">
-        <v>134</v>
+        <v>14</v>
       </c>
       <c r="E237" t="s">
-        <v>134</v>
+        <v>14</v>
       </c>
       <c r="F237" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G237">
         <v>1</v>
@@ -13297,22 +13428,22 @@
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="B238" t="s">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="C238" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D238" t="s">
-        <v>134</v>
+        <v>14</v>
       </c>
       <c r="E238" t="s">
-        <v>134</v>
+        <v>14</v>
       </c>
       <c r="F238" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G238">
         <v>1</v>
@@ -13320,22 +13451,22 @@
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="B239" t="s">
-        <v>286</v>
+        <v>221</v>
       </c>
       <c r="C239" t="s">
         <v>292</v>
       </c>
       <c r="D239" t="s">
-        <v>134</v>
+        <v>14</v>
       </c>
       <c r="E239" t="s">
-        <v>134</v>
+        <v>14</v>
       </c>
       <c r="F239" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G239">
         <v>1</v>
@@ -13343,22 +13474,22 @@
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="B240" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="C240" t="s">
         <v>292</v>
       </c>
       <c r="D240" t="s">
-        <v>134</v>
+        <v>14</v>
       </c>
       <c r="E240" t="s">
-        <v>134</v>
+        <v>14</v>
       </c>
       <c r="F240" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G240">
         <v>1</v>
@@ -13366,22 +13497,22 @@
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="B241" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="C241" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D241" t="s">
-        <v>134</v>
+        <v>14</v>
       </c>
       <c r="E241" t="s">
-        <v>134</v>
+        <v>14</v>
       </c>
       <c r="F241" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G241">
         <v>1</v>
@@ -13389,45 +13520,45 @@
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="B242" t="s">
-        <v>202</v>
+        <v>227</v>
       </c>
       <c r="C242" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D242" t="s">
-        <v>134</v>
+        <v>14</v>
       </c>
       <c r="E242" t="s">
-        <v>134</v>
+        <v>14</v>
       </c>
       <c r="F242" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G242">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="B243" t="s">
-        <v>191</v>
+        <v>219</v>
       </c>
       <c r="C243" t="s">
         <v>292</v>
       </c>
       <c r="D243" t="s">
-        <v>134</v>
+        <v>14</v>
       </c>
       <c r="E243" t="s">
-        <v>134</v>
+        <v>14</v>
       </c>
       <c r="F243" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G243">
         <v>1</v>
@@ -13435,22 +13566,22 @@
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="B244" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C244" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="D244" t="s">
-        <v>134</v>
+        <v>14</v>
       </c>
       <c r="E244" t="s">
-        <v>134</v>
+        <v>14</v>
       </c>
       <c r="F244" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G244">
         <v>1</v>
@@ -13458,22 +13589,22 @@
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="B245" t="s">
-        <v>276</v>
+        <v>230</v>
       </c>
       <c r="C245" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D245" t="s">
-        <v>134</v>
+        <v>14</v>
       </c>
       <c r="E245" t="s">
-        <v>134</v>
+        <v>14</v>
       </c>
       <c r="F245" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G245">
         <v>1</v>
@@ -13481,22 +13612,22 @@
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="B246" t="s">
-        <v>230</v>
+        <v>193</v>
       </c>
       <c r="C246" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="D246" t="s">
-        <v>134</v>
+        <v>14</v>
       </c>
       <c r="E246" t="s">
-        <v>134</v>
+        <v>14</v>
       </c>
       <c r="F246" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G246">
         <v>1</v>
@@ -13504,22 +13635,22 @@
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="B247" t="s">
-        <v>285</v>
+        <v>69</v>
       </c>
       <c r="C247" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D247" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="E247" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="F247" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G247">
         <v>1</v>
@@ -13527,22 +13658,22 @@
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>198</v>
+        <v>5</v>
       </c>
       <c r="B248" t="s">
-        <v>169</v>
+        <v>220</v>
       </c>
       <c r="C248" t="s">
         <v>292</v>
       </c>
       <c r="D248" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="E248" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="F248" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G248">
         <v>1</v>
@@ -13550,22 +13681,22 @@
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>148</v>
+        <v>5</v>
       </c>
       <c r="B249" t="s">
-        <v>69</v>
+        <v>227</v>
       </c>
       <c r="C249" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D249" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="E249" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="F249" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G249">
         <v>1</v>
@@ -13573,22 +13704,22 @@
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>148</v>
+        <v>5</v>
       </c>
       <c r="B250" t="s">
-        <v>149</v>
+        <v>219</v>
       </c>
       <c r="C250" t="s">
         <v>292</v>
       </c>
       <c r="D250" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="E250" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="F250" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G250">
         <v>1</v>
@@ -13596,7 +13727,7 @@
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="B251" t="s">
         <v>88</v>
@@ -13605,10 +13736,10 @@
         <v>293</v>
       </c>
       <c r="D251" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="E251" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="F251" t="s">
         <v>302</v>
@@ -13619,22 +13750,22 @@
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>288</v>
+        <v>5</v>
       </c>
       <c r="B252" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="C252" t="s">
         <v>293</v>
       </c>
       <c r="D252" t="s">
-        <v>287</v>
+        <v>134</v>
       </c>
       <c r="E252" t="s">
-        <v>287</v>
+        <v>134</v>
       </c>
       <c r="F252" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G252">
         <v>1</v>
@@ -13645,19 +13776,19 @@
         <v>5</v>
       </c>
       <c r="B253" t="s">
-        <v>88</v>
+        <v>272</v>
       </c>
       <c r="C253" t="s">
         <v>293</v>
       </c>
       <c r="D253" t="s">
-        <v>287</v>
+        <v>134</v>
       </c>
       <c r="E253" t="s">
-        <v>287</v>
+        <v>134</v>
       </c>
       <c r="F253" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G253">
         <v>1</v>
@@ -13665,22 +13796,22 @@
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>148</v>
+        <v>5</v>
       </c>
       <c r="B254" t="s">
-        <v>88</v>
+        <v>175</v>
       </c>
       <c r="C254" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D254" t="s">
-        <v>287</v>
+        <v>134</v>
       </c>
       <c r="E254" t="s">
-        <v>287</v>
+        <v>134</v>
       </c>
       <c r="F254" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G254">
         <v>1</v>
@@ -13688,19 +13819,19 @@
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>105</v>
+        <v>5</v>
       </c>
       <c r="B255" t="s">
-        <v>106</v>
+        <v>220</v>
       </c>
       <c r="C255" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D255" t="s">
-        <v>245</v>
+        <v>134</v>
       </c>
       <c r="E255" t="s">
-        <v>245</v>
+        <v>134</v>
       </c>
       <c r="F255" t="s">
         <v>303</v>
@@ -13711,19 +13842,19 @@
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>265</v>
+        <v>5</v>
       </c>
       <c r="B256" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="C256" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D256" t="s">
-        <v>256</v>
+        <v>134</v>
       </c>
       <c r="E256" t="s">
-        <v>261</v>
+        <v>134</v>
       </c>
       <c r="F256" t="s">
         <v>303</v>
@@ -13734,42 +13865,42 @@
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>201</v>
+        <v>5</v>
       </c>
       <c r="B257" t="s">
-        <v>179</v>
+        <v>227</v>
       </c>
       <c r="C257" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D257" t="s">
-        <v>256</v>
+        <v>134</v>
       </c>
       <c r="E257" t="s">
-        <v>261</v>
+        <v>134</v>
       </c>
       <c r="F257" t="s">
         <v>303</v>
       </c>
       <c r="G257">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>182</v>
+        <v>5</v>
       </c>
       <c r="B258" t="s">
-        <v>255</v>
+        <v>219</v>
       </c>
       <c r="C258" t="s">
         <v>292</v>
       </c>
       <c r="D258" t="s">
-        <v>256</v>
+        <v>134</v>
       </c>
       <c r="E258" t="s">
-        <v>261</v>
+        <v>134</v>
       </c>
       <c r="F258" t="s">
         <v>303</v>
@@ -13780,19 +13911,19 @@
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>182</v>
+        <v>5</v>
       </c>
       <c r="B259" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="C259" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D259" t="s">
-        <v>256</v>
+        <v>134</v>
       </c>
       <c r="E259" t="s">
-        <v>261</v>
+        <v>134</v>
       </c>
       <c r="F259" t="s">
         <v>303</v>
@@ -13803,22 +13934,22 @@
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>182</v>
+        <v>5</v>
       </c>
       <c r="B260" t="s">
-        <v>258</v>
+        <v>88</v>
       </c>
       <c r="C260" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D260" t="s">
-        <v>256</v>
+        <v>287</v>
       </c>
       <c r="E260" t="s">
-        <v>261</v>
+        <v>287</v>
       </c>
       <c r="F260" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G260">
         <v>1</v>
@@ -13826,19 +13957,19 @@
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>182</v>
+        <v>5</v>
       </c>
       <c r="B261" t="s">
-        <v>257</v>
+        <v>272</v>
       </c>
       <c r="C261" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D261" t="s">
-        <v>256</v>
+        <v>162</v>
       </c>
       <c r="E261" t="s">
-        <v>261</v>
+        <v>162</v>
       </c>
       <c r="F261" t="s">
         <v>303</v>
@@ -13849,19 +13980,19 @@
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>182</v>
+        <v>5</v>
       </c>
       <c r="B262" t="s">
-        <v>259</v>
+        <v>175</v>
       </c>
       <c r="C262" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D262" t="s">
-        <v>256</v>
+        <v>162</v>
       </c>
       <c r="E262" t="s">
-        <v>261</v>
+        <v>162</v>
       </c>
       <c r="F262" t="s">
         <v>303</v>
@@ -13872,19 +14003,19 @@
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>264</v>
+        <v>5</v>
       </c>
       <c r="B263" t="s">
-        <v>262</v>
+        <v>172</v>
       </c>
       <c r="C263" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D263" t="s">
-        <v>261</v>
+        <v>162</v>
       </c>
       <c r="E263" t="s">
-        <v>261</v>
+        <v>162</v>
       </c>
       <c r="F263" t="s">
         <v>303</v>
@@ -13895,19 +14026,19 @@
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>264</v>
+        <v>5</v>
       </c>
       <c r="B264" t="s">
-        <v>260</v>
+        <v>227</v>
       </c>
       <c r="C264" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D264" t="s">
-        <v>261</v>
+        <v>162</v>
       </c>
       <c r="E264" t="s">
-        <v>261</v>
+        <v>162</v>
       </c>
       <c r="F264" t="s">
         <v>303</v>
@@ -13918,19 +14049,19 @@
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>264</v>
+        <v>5</v>
       </c>
       <c r="B265" t="s">
-        <v>263</v>
+        <v>230</v>
       </c>
       <c r="C265" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D265" t="s">
-        <v>261</v>
+        <v>162</v>
       </c>
       <c r="E265" t="s">
-        <v>261</v>
+        <v>162</v>
       </c>
       <c r="F265" t="s">
         <v>303</v>
@@ -13941,22 +14072,22 @@
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>264</v>
+        <v>5</v>
       </c>
       <c r="B266" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="C266" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D266" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="E266" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="F266" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="G266">
         <v>1</v>
@@ -13964,22 +14095,22 @@
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>201</v>
+        <v>5</v>
       </c>
       <c r="B267" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="C267" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D267" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="E267" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="F267" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="G267">
         <v>1</v>
@@ -13987,22 +14118,22 @@
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>201</v>
+        <v>5</v>
       </c>
       <c r="B268" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="C268" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D268" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="E268" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="F268" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="G268">
         <v>1</v>
@@ -14010,22 +14141,22 @@
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>201</v>
+        <v>5</v>
       </c>
       <c r="B269" t="s">
-        <v>263</v>
+        <v>227</v>
       </c>
       <c r="C269" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D269" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="E269" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="F269" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="G269">
         <v>1</v>
@@ -14033,22 +14164,22 @@
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>201</v>
+        <v>5</v>
       </c>
       <c r="B270" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="C270" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D270" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="E270" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="F270" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="G270">
         <v>1</v>
@@ -14056,22 +14187,22 @@
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>152</v>
+        <v>5</v>
       </c>
       <c r="B271" t="s">
-        <v>157</v>
+        <v>270</v>
       </c>
       <c r="C271" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D271" t="s">
-        <v>209</v>
+        <v>268</v>
       </c>
       <c r="E271" t="s">
-        <v>209</v>
+        <v>274</v>
       </c>
       <c r="F271" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="G271">
         <v>1</v>
@@ -14079,22 +14210,22 @@
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>152</v>
+        <v>5</v>
       </c>
       <c r="B272" t="s">
-        <v>169</v>
+        <v>230</v>
       </c>
       <c r="C272" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D272" t="s">
-        <v>194</v>
+        <v>268</v>
       </c>
       <c r="E272" t="s">
-        <v>194</v>
+        <v>274</v>
       </c>
       <c r="F272" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="G272">
         <v>1</v>
@@ -14102,22 +14233,22 @@
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>195</v>
+        <v>5</v>
       </c>
       <c r="B273" t="s">
-        <v>169</v>
+        <v>193</v>
       </c>
       <c r="C273" t="s">
         <v>292</v>
       </c>
       <c r="D273" t="s">
-        <v>194</v>
+        <v>268</v>
       </c>
       <c r="E273" t="s">
-        <v>194</v>
+        <v>274</v>
       </c>
       <c r="F273" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="G273">
         <v>1</v>
@@ -14125,22 +14256,22 @@
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>196</v>
+        <v>138</v>
       </c>
       <c r="B274" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="C274" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D274" t="s">
-        <v>194</v>
+        <v>134</v>
       </c>
       <c r="E274" t="s">
-        <v>194</v>
+        <v>134</v>
       </c>
       <c r="F274" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G274">
         <v>1</v>
@@ -14148,19 +14279,19 @@
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>197</v>
+        <v>241</v>
       </c>
       <c r="B275" t="s">
-        <v>169</v>
+        <v>17</v>
       </c>
       <c r="C275" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D275" t="s">
-        <v>194</v>
+        <v>14</v>
       </c>
       <c r="E275" t="s">
-        <v>194</v>
+        <v>14</v>
       </c>
       <c r="F275" t="s">
         <v>302</v>
@@ -14171,19 +14302,19 @@
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>109</v>
+        <v>241</v>
       </c>
       <c r="B276" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="C276" t="s">
         <v>292</v>
       </c>
       <c r="D276" t="s">
-        <v>194</v>
+        <v>130</v>
       </c>
       <c r="E276" t="s">
-        <v>194</v>
+        <v>130</v>
       </c>
       <c r="F276" t="s">
         <v>302</v>
@@ -14194,19 +14325,19 @@
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>109</v>
+        <v>241</v>
       </c>
       <c r="B277" t="s">
-        <v>207</v>
+        <v>239</v>
       </c>
       <c r="C277" t="s">
         <v>292</v>
       </c>
       <c r="D277" t="s">
-        <v>194</v>
+        <v>130</v>
       </c>
       <c r="E277" t="s">
-        <v>194</v>
+        <v>130</v>
       </c>
       <c r="F277" t="s">
         <v>302</v>
@@ -14217,19 +14348,19 @@
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>109</v>
+        <v>241</v>
       </c>
       <c r="B278" t="s">
-        <v>193</v>
+        <v>240</v>
       </c>
       <c r="C278" t="s">
         <v>292</v>
       </c>
       <c r="D278" t="s">
-        <v>194</v>
+        <v>130</v>
       </c>
       <c r="E278" t="s">
-        <v>194</v>
+        <v>130</v>
       </c>
       <c r="F278" t="s">
         <v>302</v>
@@ -14240,19 +14371,19 @@
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>109</v>
+        <v>241</v>
       </c>
       <c r="B279" t="s">
-        <v>277</v>
+        <v>238</v>
       </c>
       <c r="C279" t="s">
         <v>292</v>
       </c>
       <c r="D279" t="s">
-        <v>194</v>
+        <v>130</v>
       </c>
       <c r="E279" t="s">
-        <v>194</v>
+        <v>130</v>
       </c>
       <c r="F279" t="s">
         <v>302</v>
@@ -14263,19 +14394,19 @@
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>45</v>
+        <v>241</v>
       </c>
       <c r="B280" t="s">
-        <v>157</v>
+        <v>237</v>
       </c>
       <c r="C280" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D280" t="s">
-        <v>209</v>
+        <v>130</v>
       </c>
       <c r="E280" t="s">
-        <v>209</v>
+        <v>130</v>
       </c>
       <c r="F280" t="s">
         <v>302</v>
@@ -14286,19 +14417,19 @@
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>198</v>
+        <v>109</v>
       </c>
       <c r="B281" t="s">
-        <v>169</v>
+        <v>17</v>
       </c>
       <c r="C281" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D281" t="s">
-        <v>194</v>
+        <v>14</v>
       </c>
       <c r="E281" t="s">
-        <v>194</v>
+        <v>14</v>
       </c>
       <c r="F281" t="s">
         <v>302</v>
@@ -14309,19 +14440,19 @@
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="B282" t="s">
-        <v>81</v>
+        <v>204</v>
       </c>
       <c r="C282" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D282" t="s">
-        <v>214</v>
+        <v>14</v>
       </c>
       <c r="E282" t="s">
-        <v>214</v>
+        <v>14</v>
       </c>
       <c r="F282" t="s">
         <v>302</v>
@@ -14332,19 +14463,19 @@
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>144</v>
+        <v>109</v>
       </c>
       <c r="B283" t="s">
-        <v>145</v>
+        <v>207</v>
       </c>
       <c r="C283" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D283" t="s">
-        <v>214</v>
+        <v>14</v>
       </c>
       <c r="E283" t="s">
-        <v>214</v>
+        <v>14</v>
       </c>
       <c r="F283" t="s">
         <v>302</v>
@@ -14355,19 +14486,19 @@
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>60</v>
+        <v>109</v>
       </c>
       <c r="B284" t="s">
-        <v>84</v>
+        <v>193</v>
       </c>
       <c r="C284" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D284" t="s">
-        <v>214</v>
+        <v>14</v>
       </c>
       <c r="E284" t="s">
-        <v>214</v>
+        <v>14</v>
       </c>
       <c r="F284" t="s">
         <v>302</v>
@@ -14378,22 +14509,22 @@
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>152</v>
+        <v>109</v>
       </c>
       <c r="B285" t="s">
-        <v>169</v>
+        <v>277</v>
       </c>
       <c r="C285" t="s">
         <v>292</v>
       </c>
       <c r="D285" t="s">
-        <v>162</v>
+        <v>14</v>
       </c>
       <c r="E285" t="s">
-        <v>162</v>
+        <v>14</v>
       </c>
       <c r="F285" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G285">
         <v>1</v>
@@ -14401,22 +14532,22 @@
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>195</v>
+        <v>109</v>
       </c>
       <c r="B286" t="s">
-        <v>169</v>
+        <v>204</v>
       </c>
       <c r="C286" t="s">
         <v>292</v>
       </c>
       <c r="D286" t="s">
-        <v>162</v>
+        <v>278</v>
       </c>
       <c r="E286" t="s">
-        <v>162</v>
+        <v>278</v>
       </c>
       <c r="F286" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G286">
         <v>1</v>
@@ -14424,22 +14555,22 @@
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>160</v>
+        <v>109</v>
       </c>
       <c r="B287" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="C287" t="s">
         <v>292</v>
       </c>
       <c r="D287" t="s">
-        <v>162</v>
+        <v>278</v>
       </c>
       <c r="E287" t="s">
-        <v>162</v>
+        <v>278</v>
       </c>
       <c r="F287" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G287">
         <v>1</v>
@@ -14447,22 +14578,22 @@
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>160</v>
+        <v>109</v>
       </c>
       <c r="B288" t="s">
-        <v>216</v>
+        <v>193</v>
       </c>
       <c r="C288" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D288" t="s">
-        <v>162</v>
+        <v>278</v>
       </c>
       <c r="E288" t="s">
-        <v>162</v>
+        <v>278</v>
       </c>
       <c r="F288" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G288">
         <v>1</v>
@@ -14470,22 +14601,22 @@
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>264</v>
+        <v>109</v>
       </c>
       <c r="B289" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="C289" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D289" t="s">
-        <v>162</v>
+        <v>278</v>
       </c>
       <c r="E289" t="s">
-        <v>162</v>
+        <v>278</v>
       </c>
       <c r="F289" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G289">
         <v>1</v>
@@ -14493,22 +14624,22 @@
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>264</v>
+        <v>109</v>
       </c>
       <c r="B290" t="s">
-        <v>260</v>
+        <v>204</v>
       </c>
       <c r="C290" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D290" t="s">
-        <v>162</v>
+        <v>194</v>
       </c>
       <c r="E290" t="s">
-        <v>162</v>
+        <v>194</v>
       </c>
       <c r="F290" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G290">
         <v>1</v>
@@ -14516,22 +14647,22 @@
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>264</v>
+        <v>109</v>
       </c>
       <c r="B291" t="s">
-        <v>263</v>
+        <v>207</v>
       </c>
       <c r="C291" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D291" t="s">
-        <v>162</v>
+        <v>194</v>
       </c>
       <c r="E291" t="s">
-        <v>162</v>
+        <v>194</v>
       </c>
       <c r="F291" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G291">
         <v>1</v>
@@ -14539,22 +14670,22 @@
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>264</v>
+        <v>109</v>
       </c>
       <c r="B292" t="s">
-        <v>258</v>
+        <v>193</v>
       </c>
       <c r="C292" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D292" t="s">
-        <v>162</v>
+        <v>194</v>
       </c>
       <c r="E292" t="s">
-        <v>162</v>
+        <v>194</v>
       </c>
       <c r="F292" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G292">
         <v>1</v>
@@ -14562,22 +14693,22 @@
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>265</v>
+        <v>109</v>
       </c>
       <c r="B293" t="s">
-        <v>179</v>
+        <v>277</v>
       </c>
       <c r="C293" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D293" t="s">
-        <v>162</v>
+        <v>194</v>
       </c>
       <c r="E293" t="s">
-        <v>162</v>
+        <v>194</v>
       </c>
       <c r="F293" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G293">
         <v>1</v>
@@ -14585,22 +14716,22 @@
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B294" t="s">
-        <v>113</v>
+        <v>205</v>
       </c>
       <c r="C294" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D294" t="s">
-        <v>162</v>
+        <v>14</v>
       </c>
       <c r="E294" t="s">
-        <v>162</v>
+        <v>14</v>
       </c>
       <c r="F294" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G294">
         <v>1</v>
@@ -14608,22 +14739,22 @@
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>164</v>
+        <v>45</v>
       </c>
       <c r="B295" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="C295" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D295" t="s">
-        <v>162</v>
+        <v>14</v>
       </c>
       <c r="E295" t="s">
-        <v>162</v>
+        <v>14</v>
       </c>
       <c r="F295" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G295">
         <v>1</v>
@@ -14631,22 +14762,22 @@
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>164</v>
+        <v>45</v>
       </c>
       <c r="B296" t="s">
-        <v>243</v>
+        <v>157</v>
       </c>
       <c r="C296" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D296" t="s">
-        <v>162</v>
+        <v>14</v>
       </c>
       <c r="E296" t="s">
-        <v>162</v>
+        <v>14</v>
       </c>
       <c r="F296" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G296">
         <v>1</v>
@@ -14654,22 +14785,22 @@
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>105</v>
+        <v>45</v>
       </c>
       <c r="B297" t="s">
-        <v>116</v>
+        <v>284</v>
       </c>
       <c r="C297" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D297" t="s">
-        <v>162</v>
+        <v>14</v>
       </c>
       <c r="E297" t="s">
-        <v>162</v>
+        <v>14</v>
       </c>
       <c r="F297" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G297">
         <v>1</v>
@@ -14677,22 +14808,22 @@
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>196</v>
+        <v>45</v>
       </c>
       <c r="B298" t="s">
-        <v>169</v>
+        <v>286</v>
       </c>
       <c r="C298" t="s">
         <v>292</v>
       </c>
       <c r="D298" t="s">
-        <v>162</v>
+        <v>14</v>
       </c>
       <c r="E298" t="s">
-        <v>162</v>
+        <v>14</v>
       </c>
       <c r="F298" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G298">
         <v>1</v>
@@ -14700,22 +14831,22 @@
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>197</v>
+        <v>45</v>
       </c>
       <c r="B299" t="s">
-        <v>169</v>
+        <v>204</v>
       </c>
       <c r="C299" t="s">
         <v>292</v>
       </c>
       <c r="D299" t="s">
-        <v>162</v>
+        <v>14</v>
       </c>
       <c r="E299" t="s">
-        <v>162</v>
+        <v>14</v>
       </c>
       <c r="F299" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G299">
         <v>1</v>
@@ -14723,22 +14854,22 @@
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>201</v>
+        <v>45</v>
       </c>
       <c r="B300" t="s">
-        <v>179</v>
+        <v>282</v>
       </c>
       <c r="C300" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D300" t="s">
-        <v>162</v>
+        <v>14</v>
       </c>
       <c r="E300" t="s">
-        <v>162</v>
+        <v>14</v>
       </c>
       <c r="F300" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G300">
         <v>1</v>
@@ -14746,22 +14877,22 @@
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>201</v>
+        <v>45</v>
       </c>
       <c r="B301" t="s">
-        <v>262</v>
+        <v>280</v>
       </c>
       <c r="C301" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D301" t="s">
-        <v>162</v>
+        <v>14</v>
       </c>
       <c r="E301" t="s">
-        <v>162</v>
+        <v>14</v>
       </c>
       <c r="F301" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G301">
         <v>1</v>
@@ -14769,22 +14900,22 @@
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>201</v>
+        <v>45</v>
       </c>
       <c r="B302" t="s">
-        <v>260</v>
+        <v>283</v>
       </c>
       <c r="C302" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D302" t="s">
-        <v>162</v>
+        <v>14</v>
       </c>
       <c r="E302" t="s">
-        <v>162</v>
+        <v>14</v>
       </c>
       <c r="F302" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G302">
         <v>1</v>
@@ -14792,22 +14923,22 @@
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>201</v>
+        <v>45</v>
       </c>
       <c r="B303" t="s">
-        <v>263</v>
+        <v>40</v>
       </c>
       <c r="C303" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D303" t="s">
-        <v>162</v>
+        <v>14</v>
       </c>
       <c r="E303" t="s">
-        <v>162</v>
+        <v>14</v>
       </c>
       <c r="F303" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G303">
         <v>1</v>
@@ -14815,22 +14946,22 @@
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>201</v>
+        <v>45</v>
       </c>
       <c r="B304" t="s">
-        <v>258</v>
+        <v>279</v>
       </c>
       <c r="C304" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D304" t="s">
-        <v>162</v>
+        <v>14</v>
       </c>
       <c r="E304" t="s">
-        <v>162</v>
+        <v>14</v>
       </c>
       <c r="F304" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G304">
         <v>1</v>
@@ -14838,22 +14969,22 @@
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>182</v>
+        <v>45</v>
       </c>
       <c r="B305" t="s">
-        <v>255</v>
+        <v>276</v>
       </c>
       <c r="C305" t="s">
         <v>292</v>
       </c>
       <c r="D305" t="s">
-        <v>162</v>
+        <v>14</v>
       </c>
       <c r="E305" t="s">
-        <v>162</v>
+        <v>14</v>
       </c>
       <c r="F305" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G305">
         <v>1</v>
@@ -14861,22 +14992,22 @@
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>182</v>
+        <v>45</v>
       </c>
       <c r="B306" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="C306" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D306" t="s">
-        <v>162</v>
+        <v>14</v>
       </c>
       <c r="E306" t="s">
-        <v>162</v>
+        <v>14</v>
       </c>
       <c r="F306" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G306">
         <v>1</v>
@@ -14884,22 +15015,22 @@
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>182</v>
+        <v>45</v>
       </c>
       <c r="B307" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="C307" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D307" t="s">
-        <v>162</v>
+        <v>14</v>
       </c>
       <c r="E307" t="s">
-        <v>162</v>
+        <v>14</v>
       </c>
       <c r="F307" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G307">
         <v>1</v>
@@ -14907,22 +15038,22 @@
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>182</v>
+        <v>45</v>
       </c>
       <c r="B308" t="s">
-        <v>257</v>
+        <v>281</v>
       </c>
       <c r="C308" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D308" t="s">
-        <v>162</v>
+        <v>14</v>
       </c>
       <c r="E308" t="s">
-        <v>162</v>
+        <v>14</v>
       </c>
       <c r="F308" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G308">
         <v>1</v>
@@ -14930,22 +15061,22 @@
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>182</v>
+        <v>45</v>
       </c>
       <c r="B309" t="s">
-        <v>259</v>
+        <v>286</v>
       </c>
       <c r="C309" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D309" t="s">
-        <v>162</v>
+        <v>278</v>
       </c>
       <c r="E309" t="s">
-        <v>162</v>
+        <v>278</v>
       </c>
       <c r="F309" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G309">
         <v>1</v>
@@ -14953,22 +15084,22 @@
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="B310" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="C310" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D310" t="s">
-        <v>162</v>
+        <v>278</v>
       </c>
       <c r="E310" t="s">
-        <v>162</v>
+        <v>278</v>
       </c>
       <c r="F310" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G310">
         <v>1</v>
@@ -14976,19 +15107,19 @@
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="B311" t="s">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C311" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D311" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="E311" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="F311" t="s">
         <v>303</v>
@@ -14999,19 +15130,19 @@
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="B312" t="s">
-        <v>172</v>
+        <v>192</v>
       </c>
       <c r="C312" t="s">
         <v>292</v>
       </c>
       <c r="D312" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="E312" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="F312" t="s">
         <v>303</v>
@@ -15022,19 +15153,19 @@
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="B313" t="s">
-        <v>227</v>
+        <v>286</v>
       </c>
       <c r="C313" t="s">
         <v>292</v>
       </c>
       <c r="D313" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="E313" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="F313" t="s">
         <v>303</v>
@@ -15045,19 +15176,19 @@
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="B314" t="s">
-        <v>230</v>
+        <v>204</v>
       </c>
       <c r="C314" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="D314" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="E314" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="F314" t="s">
         <v>303</v>
@@ -15068,19 +15199,19 @@
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>198</v>
+        <v>45</v>
       </c>
       <c r="B315" t="s">
-        <v>169</v>
+        <v>280</v>
       </c>
       <c r="C315" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D315" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="E315" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="F315" t="s">
         <v>303</v>
@@ -15091,19 +15222,19 @@
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>148</v>
+        <v>45</v>
       </c>
       <c r="B316" t="s">
-        <v>149</v>
+        <v>202</v>
       </c>
       <c r="C316" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D316" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="E316" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="F316" t="s">
         <v>303</v>
@@ -15114,22 +15245,22 @@
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="B317" t="s">
-        <v>84</v>
+        <v>191</v>
       </c>
       <c r="C317" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D317" t="s">
-        <v>222</v>
+        <v>134</v>
       </c>
       <c r="E317" t="s">
-        <v>222</v>
+        <v>134</v>
       </c>
       <c r="F317" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G317">
         <v>1</v>
@@ -15137,22 +15268,22 @@
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>118</v>
+        <v>45</v>
       </c>
       <c r="B318" t="s">
-        <v>224</v>
+        <v>279</v>
       </c>
       <c r="C318" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D318" t="s">
-        <v>225</v>
+        <v>134</v>
       </c>
       <c r="E318" t="s">
-        <v>225</v>
+        <v>134</v>
       </c>
       <c r="F318" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="G318">
         <v>1</v>
@@ -15160,22 +15291,22 @@
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>118</v>
+        <v>45</v>
       </c>
       <c r="B319" t="s">
-        <v>226</v>
+        <v>276</v>
       </c>
       <c r="C319" t="s">
         <v>292</v>
       </c>
       <c r="D319" t="s">
-        <v>225</v>
+        <v>134</v>
       </c>
       <c r="E319" t="s">
-        <v>225</v>
+        <v>134</v>
       </c>
       <c r="F319" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="G319">
         <v>1</v>
@@ -15183,22 +15314,22 @@
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>118</v>
+        <v>45</v>
       </c>
       <c r="B320" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C320" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D320" t="s">
-        <v>225</v>
+        <v>134</v>
       </c>
       <c r="E320" t="s">
-        <v>225</v>
+        <v>134</v>
       </c>
       <c r="F320" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="G320">
         <v>1</v>
@@ -15206,22 +15337,22 @@
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>118</v>
+        <v>45</v>
       </c>
       <c r="B321" t="s">
-        <v>228</v>
+        <v>285</v>
       </c>
       <c r="C321" t="s">
         <v>296</v>
       </c>
       <c r="D321" t="s">
-        <v>225</v>
+        <v>134</v>
       </c>
       <c r="E321" t="s">
-        <v>225</v>
+        <v>134</v>
       </c>
       <c r="F321" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="G321">
         <v>1</v>
@@ -15229,22 +15360,22 @@
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>118</v>
+        <v>45</v>
       </c>
       <c r="B322" t="s">
-        <v>193</v>
+        <v>157</v>
       </c>
       <c r="C322" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D322" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="E322" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="F322" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="G322">
         <v>1</v>
@@ -15252,22 +15383,22 @@
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>152</v>
+        <v>198</v>
       </c>
       <c r="B323" t="s">
-        <v>192</v>
+        <v>169</v>
       </c>
       <c r="C323" t="s">
         <v>292</v>
       </c>
       <c r="D323" t="s">
-        <v>190</v>
+        <v>14</v>
       </c>
       <c r="E323" t="s">
-        <v>190</v>
+        <v>14</v>
       </c>
       <c r="F323" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="G323">
         <v>1</v>
@@ -15275,22 +15406,22 @@
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>152</v>
+        <v>198</v>
       </c>
       <c r="B324" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="C324" t="s">
         <v>292</v>
       </c>
       <c r="D324" t="s">
-        <v>190</v>
+        <v>134</v>
       </c>
       <c r="E324" t="s">
-        <v>190</v>
+        <v>134</v>
       </c>
       <c r="F324" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G324">
         <v>1</v>
@@ -15298,22 +15429,22 @@
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>152</v>
+        <v>198</v>
       </c>
       <c r="B325" t="s">
-        <v>191</v>
+        <v>169</v>
       </c>
       <c r="C325" t="s">
         <v>292</v>
       </c>
       <c r="D325" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="E325" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="F325" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="G325">
         <v>1</v>
@@ -15321,22 +15452,22 @@
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>152</v>
+        <v>198</v>
       </c>
       <c r="B326" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="C326" t="s">
         <v>292</v>
       </c>
       <c r="D326" t="s">
-        <v>190</v>
+        <v>162</v>
       </c>
       <c r="E326" t="s">
-        <v>190</v>
+        <v>162</v>
       </c>
       <c r="F326" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G326">
         <v>1</v>
@@ -15344,22 +15475,22 @@
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>5</v>
+        <v>148</v>
       </c>
       <c r="B327" t="s">
-        <v>266</v>
+        <v>88</v>
       </c>
       <c r="C327" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D327" t="s">
-        <v>268</v>
+        <v>14</v>
       </c>
       <c r="E327" t="s">
-        <v>274</v>
+        <v>14</v>
       </c>
       <c r="F327" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="G327">
         <v>1</v>
@@ -15367,22 +15498,22 @@
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>5</v>
+        <v>148</v>
       </c>
       <c r="B328" t="s">
-        <v>272</v>
+        <v>69</v>
       </c>
       <c r="C328" t="s">
         <v>293</v>
       </c>
       <c r="D328" t="s">
-        <v>268</v>
+        <v>14</v>
       </c>
       <c r="E328" t="s">
-        <v>274</v>
+        <v>14</v>
       </c>
       <c r="F328" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="G328">
         <v>1</v>
@@ -15390,22 +15521,22 @@
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>5</v>
+        <v>148</v>
       </c>
       <c r="B329" t="s">
-        <v>271</v>
+        <v>69</v>
       </c>
       <c r="C329" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D329" t="s">
-        <v>268</v>
+        <v>124</v>
       </c>
       <c r="E329" t="s">
-        <v>274</v>
+        <v>124</v>
       </c>
       <c r="F329" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="G329">
         <v>1</v>
@@ -15413,22 +15544,22 @@
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>5</v>
+        <v>148</v>
       </c>
       <c r="B330" t="s">
-        <v>227</v>
+        <v>88</v>
       </c>
       <c r="C330" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D330" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="E330" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="F330" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="G330">
         <v>1</v>
@@ -15436,22 +15567,22 @@
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>5</v>
+        <v>148</v>
       </c>
       <c r="B331" t="s">
-        <v>269</v>
+        <v>69</v>
       </c>
       <c r="C331" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D331" t="s">
-        <v>268</v>
+        <v>134</v>
       </c>
       <c r="E331" t="s">
-        <v>274</v>
+        <v>134</v>
       </c>
       <c r="F331" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="G331">
         <v>1</v>
@@ -15459,22 +15590,22 @@
     </row>
     <row r="332" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>5</v>
+        <v>148</v>
       </c>
       <c r="B332" t="s">
-        <v>270</v>
+        <v>149</v>
       </c>
       <c r="C332" t="s">
         <v>292</v>
       </c>
       <c r="D332" t="s">
-        <v>268</v>
+        <v>134</v>
       </c>
       <c r="E332" t="s">
-        <v>274</v>
+        <v>134</v>
       </c>
       <c r="F332" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="G332">
         <v>1</v>
@@ -15482,22 +15613,22 @@
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>5</v>
+        <v>148</v>
       </c>
       <c r="B333" t="s">
-        <v>230</v>
+        <v>88</v>
       </c>
       <c r="C333" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D333" t="s">
-        <v>268</v>
+        <v>287</v>
       </c>
       <c r="E333" t="s">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="F333" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="G333">
         <v>1</v>
@@ -15505,22 +15636,22 @@
     </row>
     <row r="334" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>5</v>
+        <v>148</v>
       </c>
       <c r="B334" t="s">
-        <v>193</v>
+        <v>149</v>
       </c>
       <c r="C334" t="s">
         <v>292</v>
       </c>
       <c r="D334" t="s">
-        <v>268</v>
+        <v>162</v>
       </c>
       <c r="E334" t="s">
-        <v>274</v>
+        <v>162</v>
       </c>
       <c r="F334" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="G334">
         <v>1</v>
@@ -15529,7 +15660,7 @@
   </sheetData>
   <autoFilter ref="A1:G334" xr:uid="{00000000-0001-0000-0200-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G334">
-      <sortCondition ref="E1:E334"/>
+      <sortCondition ref="A1:A334"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
